--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212463CF-7532-49B0-B89F-BBBBF5D5DEEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CFA4C0-8F1E-4D72-9079-1473757098E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="285" windowWidth="24930" windowHeight="15105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CashShop" sheetId="1" r:id="rId1"/>
@@ -3385,12 +3385,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3405,12 +3411,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3426,9 +3433,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3466,7 +3473,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3572,7 +3579,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3854,7 +3861,7 @@
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C3">
@@ -3898,7 +3905,7 @@
       <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C4">
@@ -3942,7 +3949,7 @@
       <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C5">
@@ -3986,7 +3993,7 @@
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C6">
@@ -4030,7 +4037,7 @@
       <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C7">
@@ -4074,7 +4081,7 @@
       <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8">
@@ -4118,7 +4125,7 @@
       <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C9">
@@ -4162,7 +4169,7 @@
       <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C10">
@@ -4206,7 +4213,7 @@
       <c r="A11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C11">
@@ -4250,7 +4257,7 @@
       <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12">
@@ -4294,17 +4301,17 @@
       <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C13">
         <v>150</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -4338,17 +4345,17 @@
       <c r="A14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C14">
         <v>150</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -4382,7 +4389,7 @@
       <c r="A15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C15">
@@ -4426,17 +4433,17 @@
       <c r="A16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C16">
         <v>200</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -4470,17 +4477,17 @@
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C17">
         <v>300</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -4514,7 +4521,7 @@
       <c r="A18" t="s">
         <v>45</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C18">
@@ -4558,17 +4565,17 @@
       <c r="A19" t="s">
         <v>47</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C19">
         <v>200</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -4602,17 +4609,17 @@
       <c r="A20" t="s">
         <v>49</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C20">
         <v>300</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -4646,17 +4653,17 @@
       <c r="A21" t="s">
         <v>51</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C21">
         <v>300</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -4690,7 +4697,7 @@
       <c r="A22" t="s">
         <v>53</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C22">
@@ -4734,7 +4741,7 @@
       <c r="A23" t="s">
         <v>55</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C23">
@@ -4778,17 +4785,17 @@
       <c r="A24" t="s">
         <v>57</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C24">
         <v>300</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -4822,17 +4829,17 @@
       <c r="A25" t="s">
         <v>59</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C25">
         <v>300</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F25">
         <v>-1</v>
@@ -4866,17 +4873,17 @@
       <c r="A26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C26">
         <v>300</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F26">
         <v>-1</v>
@@ -4910,17 +4917,17 @@
       <c r="A27" t="s">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C27">
         <v>200</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -4954,17 +4961,17 @@
       <c r="A28" t="s">
         <v>65</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C28">
         <v>200</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -4998,7 +5005,7 @@
       <c r="A29" t="s">
         <v>67</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C29">
@@ -5042,17 +5049,17 @@
       <c r="A30" t="s">
         <v>69</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C30">
         <v>300</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F30">
         <v>-1</v>
@@ -5086,7 +5093,7 @@
       <c r="A31" t="s">
         <v>71</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C31">
@@ -5130,17 +5137,17 @@
       <c r="A32" t="s">
         <v>73</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C32">
         <v>200</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -5174,17 +5181,17 @@
       <c r="A33" t="s">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C33">
         <v>300</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F33">
         <v>-1</v>
@@ -5218,17 +5225,17 @@
       <c r="A34" t="s">
         <v>77</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C34">
         <v>300</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -5262,7 +5269,7 @@
       <c r="A35" t="s">
         <v>79</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C35">
@@ -5306,17 +5313,17 @@
       <c r="A36" t="s">
         <v>81</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C36">
         <v>300</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F36">
         <v>-1</v>
@@ -5350,17 +5357,17 @@
       <c r="A37" t="s">
         <v>83</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C37">
         <v>300</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F37">
         <v>-1</v>
@@ -5394,17 +5401,17 @@
       <c r="A38" t="s">
         <v>85</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C38">
         <v>300</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F38">
         <v>-1</v>
@@ -5438,17 +5445,17 @@
       <c r="A39" t="s">
         <v>87</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C39">
         <v>300</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F39">
         <v>-1</v>
@@ -5482,7 +5489,7 @@
       <c r="A40" t="s">
         <v>89</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C40">
@@ -5526,7 +5533,7 @@
       <c r="A41" t="s">
         <v>91</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C41">
@@ -5570,17 +5577,17 @@
       <c r="A42" t="s">
         <v>93</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C42">
         <v>400</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F42">
         <v>-1</v>
@@ -5614,17 +5621,17 @@
       <c r="A43" t="s">
         <v>95</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C43">
         <v>400</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F43">
         <v>-1</v>
@@ -5658,17 +5665,17 @@
       <c r="A44" t="s">
         <v>97</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C44">
         <v>400</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F44">
         <v>-1</v>
@@ -5702,17 +5709,17 @@
       <c r="A45" t="s">
         <v>99</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C45">
         <v>500</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F45">
         <v>-1</v>
@@ -5746,17 +5753,17 @@
       <c r="A46" t="s">
         <v>101</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C46">
         <v>600</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F46">
         <v>-1</v>
@@ -5790,17 +5797,17 @@
       <c r="A47" t="s">
         <v>103</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C47">
         <v>1000</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F47">
         <v>-1</v>
@@ -5834,17 +5841,17 @@
       <c r="A48" t="s">
         <v>105</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C48">
         <v>1200</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F48">
         <v>-1</v>
@@ -5878,17 +5885,17 @@
       <c r="A49" t="s">
         <v>107</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C49">
         <v>1200</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F49">
         <v>-1</v>
@@ -5922,17 +5929,17 @@
       <c r="A50" t="s">
         <v>109</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C50">
         <v>1000</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F50">
         <v>-1</v>
@@ -5966,17 +5973,17 @@
       <c r="A51" t="s">
         <v>111</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C51">
         <v>1300</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F51">
         <v>-1</v>
@@ -6010,17 +6017,17 @@
       <c r="A52" t="s">
         <v>113</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C52">
         <v>1300</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F52">
         <v>-1</v>
@@ -6054,17 +6061,17 @@
       <c r="A53" t="s">
         <v>115</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C53">
         <v>1200</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F53">
         <v>-1</v>
@@ -6098,17 +6105,17 @@
       <c r="A54" t="s">
         <v>117</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C54">
         <v>1200</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F54">
         <v>-1</v>
@@ -6142,17 +6149,17 @@
       <c r="A55" t="s">
         <v>119</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C55">
         <v>1300</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F55">
         <v>-1</v>
@@ -6186,17 +6193,17 @@
       <c r="A56" t="s">
         <v>121</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C56">
         <v>1300</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F56">
         <v>-1</v>
@@ -6230,7 +6237,7 @@
       <c r="A57" t="s">
         <v>123</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C57">
@@ -6274,7 +6281,7 @@
       <c r="A58" t="s">
         <v>125</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C58">
@@ -6318,7 +6325,7 @@
       <c r="A59" t="s">
         <v>127</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C59">
@@ -6362,7 +6369,7 @@
       <c r="A60" t="s">
         <v>129</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C60">
@@ -6406,7 +6413,7 @@
       <c r="A61" t="s">
         <v>131</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C61">
@@ -6450,7 +6457,7 @@
       <c r="A62" t="s">
         <v>133</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C62">
@@ -6494,7 +6501,7 @@
       <c r="A63" t="s">
         <v>135</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C63">
@@ -6538,7 +6545,7 @@
       <c r="A64" t="s">
         <v>137</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C64">
@@ -6582,7 +6589,7 @@
       <c r="A65" t="s">
         <v>139</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C65">
@@ -6626,7 +6633,7 @@
       <c r="A66" t="s">
         <v>141</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C66">
@@ -6670,7 +6677,7 @@
       <c r="A67" t="s">
         <v>143</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C67">
@@ -6714,7 +6721,7 @@
       <c r="A68" t="s">
         <v>145</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C68">
@@ -6758,7 +6765,7 @@
       <c r="A69" t="s">
         <v>147</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C69">
@@ -6802,7 +6809,7 @@
       <c r="A70" t="s">
         <v>149</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C70">
@@ -6846,7 +6853,7 @@
       <c r="A71" t="s">
         <v>151</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C71">
@@ -6890,7 +6897,7 @@
       <c r="A72" t="s">
         <v>153</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C72">
@@ -6934,7 +6941,7 @@
       <c r="A73" t="s">
         <v>155</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C73">
@@ -6978,7 +6985,7 @@
       <c r="A74" t="s">
         <v>157</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C74">
@@ -7022,7 +7029,7 @@
       <c r="A75" t="s">
         <v>159</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C75">
@@ -7066,7 +7073,7 @@
       <c r="A76" t="s">
         <v>161</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C76">
@@ -7110,7 +7117,7 @@
       <c r="A77" t="s">
         <v>163</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C77">
@@ -7154,7 +7161,7 @@
       <c r="A78" t="s">
         <v>165</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C78">
@@ -7198,7 +7205,7 @@
       <c r="A79" t="s">
         <v>167</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C79">
@@ -7242,7 +7249,7 @@
       <c r="A80" t="s">
         <v>169</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C80">
@@ -7286,7 +7293,7 @@
       <c r="A81" t="s">
         <v>171</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C81">
@@ -7330,7 +7337,7 @@
       <c r="A82" t="s">
         <v>173</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C82">
@@ -7374,7 +7381,7 @@
       <c r="A83" t="s">
         <v>175</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C83">
@@ -7418,7 +7425,7 @@
       <c r="A84" t="s">
         <v>177</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C84">
@@ -7462,7 +7469,7 @@
       <c r="A85" t="s">
         <v>179</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C85">
@@ -7506,17 +7513,17 @@
       <c r="A86" t="s">
         <v>181</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C86">
         <v>300</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F86">
         <v>-1</v>
@@ -7550,17 +7557,17 @@
       <c r="A87" t="s">
         <v>183</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C87">
         <v>500</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F87">
         <v>-1</v>
@@ -7594,17 +7601,17 @@
       <c r="A88" t="s">
         <v>185</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C88">
         <v>200</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F88">
         <v>-1</v>
@@ -7638,17 +7645,17 @@
       <c r="A89" t="s">
         <v>187</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C89">
         <v>200</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F89">
         <v>-1</v>
@@ -7682,7 +7689,7 @@
       <c r="A90" t="s">
         <v>189</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C90">
@@ -7726,17 +7733,17 @@
       <c r="A91" t="s">
         <v>191</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C91">
         <v>500</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F91">
         <v>-1</v>
@@ -7770,17 +7777,17 @@
       <c r="A92" t="s">
         <v>193</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C92">
         <v>500</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F92">
         <v>-1</v>
@@ -7814,7 +7821,7 @@
       <c r="A93" t="s">
         <v>195</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C93">
@@ -7858,17 +7865,17 @@
       <c r="A94" t="s">
         <v>197</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C94">
         <v>900</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F94">
         <v>-1</v>
@@ -7902,17 +7909,17 @@
       <c r="A95" t="s">
         <v>199</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C95">
         <v>900</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F95">
         <v>-1</v>
@@ -7946,7 +7953,7 @@
       <c r="A96" t="s">
         <v>201</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C96">
@@ -7990,7 +7997,7 @@
       <c r="A97" t="s">
         <v>203</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C97">
@@ -8034,7 +8041,7 @@
       <c r="A98" t="s">
         <v>206</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C98">
@@ -8078,7 +8085,7 @@
       <c r="A99" t="s">
         <v>208</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C99">
@@ -8122,7 +8129,7 @@
       <c r="A100" t="s">
         <v>211</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="2" t="s">
         <v>212</v>
       </c>
       <c r="C100">
@@ -8166,7 +8173,7 @@
       <c r="A101" t="s">
         <v>213</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C101">
@@ -8210,7 +8217,7 @@
       <c r="A102" t="s">
         <v>215</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="2" t="s">
         <v>216</v>
       </c>
       <c r="C102">
@@ -8254,7 +8261,7 @@
       <c r="A103" t="s">
         <v>217</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C103">
@@ -8298,7 +8305,7 @@
       <c r="A104" t="s">
         <v>219</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>220</v>
       </c>
       <c r="C104">
@@ -8342,7 +8349,7 @@
       <c r="A105" t="s">
         <v>221</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>222</v>
       </c>
       <c r="C105">
@@ -8386,7 +8393,7 @@
       <c r="A106" t="s">
         <v>223</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C106">
@@ -8430,7 +8437,7 @@
       <c r="A107" t="s">
         <v>225</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2" t="s">
         <v>226</v>
       </c>
       <c r="C107">
@@ -8474,7 +8481,7 @@
       <c r="A108" t="s">
         <v>227</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2" t="s">
         <v>228</v>
       </c>
       <c r="C108">
@@ -8518,7 +8525,7 @@
       <c r="A109" t="s">
         <v>229</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C109">
@@ -8562,7 +8569,7 @@
       <c r="A110" t="s">
         <v>231</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2" t="s">
         <v>232</v>
       </c>
       <c r="C110">
@@ -8606,7 +8613,7 @@
       <c r="A111" t="s">
         <v>233</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="2" t="s">
         <v>234</v>
       </c>
       <c r="C111">
@@ -8650,7 +8657,7 @@
       <c r="A112" t="s">
         <v>235</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="2" t="s">
         <v>236</v>
       </c>
       <c r="C112">
@@ -8694,7 +8701,7 @@
       <c r="A113" t="s">
         <v>237</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2" t="s">
         <v>238</v>
       </c>
       <c r="C113">
@@ -8738,7 +8745,7 @@
       <c r="A114" t="s">
         <v>239</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2" t="s">
         <v>240</v>
       </c>
       <c r="C114">
@@ -8782,7 +8789,7 @@
       <c r="A115" t="s">
         <v>241</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="2" t="s">
         <v>242</v>
       </c>
       <c r="C115">
@@ -8826,7 +8833,7 @@
       <c r="A116" t="s">
         <v>243</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="2" t="s">
         <v>244</v>
       </c>
       <c r="C116">
@@ -8870,7 +8877,7 @@
       <c r="A117" t="s">
         <v>245</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C117">
@@ -8914,7 +8921,7 @@
       <c r="A118" t="s">
         <v>247</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="2" t="s">
         <v>248</v>
       </c>
       <c r="C118">
@@ -8958,7 +8965,7 @@
       <c r="A119" t="s">
         <v>249</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="2" t="s">
         <v>250</v>
       </c>
       <c r="C119">
@@ -9002,7 +9009,7 @@
       <c r="A120" t="s">
         <v>251</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2" t="s">
         <v>252</v>
       </c>
       <c r="C120">
@@ -9046,7 +9053,7 @@
       <c r="A121" t="s">
         <v>253</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="2" t="s">
         <v>254</v>
       </c>
       <c r="C121">
@@ -9090,7 +9097,7 @@
       <c r="A122" t="s">
         <v>255</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="2" t="s">
         <v>256</v>
       </c>
       <c r="C122">
@@ -9134,7 +9141,7 @@
       <c r="A123" t="s">
         <v>257</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="2" t="s">
         <v>258</v>
       </c>
       <c r="C123">
@@ -9178,7 +9185,7 @@
       <c r="A124" t="s">
         <v>259</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="2" t="s">
         <v>260</v>
       </c>
       <c r="C124">
@@ -9222,7 +9229,7 @@
       <c r="A125" t="s">
         <v>261</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="2" t="s">
         <v>262</v>
       </c>
       <c r="C125">
@@ -9266,7 +9273,7 @@
       <c r="A126" t="s">
         <v>263</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="2" t="s">
         <v>264</v>
       </c>
       <c r="C126">
@@ -9310,7 +9317,7 @@
       <c r="A127" t="s">
         <v>265</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C127">
@@ -9354,7 +9361,7 @@
       <c r="A128" t="s">
         <v>267</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="2" t="s">
         <v>268</v>
       </c>
       <c r="C128">
@@ -9398,7 +9405,7 @@
       <c r="A129" t="s">
         <v>269</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C129">
@@ -9442,7 +9449,7 @@
       <c r="A130" t="s">
         <v>271</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="2" t="s">
         <v>272</v>
       </c>
       <c r="C130">
@@ -9486,7 +9493,7 @@
       <c r="A131" t="s">
         <v>273</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="2" t="s">
         <v>274</v>
       </c>
       <c r="C131">
@@ -9530,7 +9537,7 @@
       <c r="A132" t="s">
         <v>275</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C132">
@@ -9574,7 +9581,7 @@
       <c r="A133" t="s">
         <v>277</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="2" t="s">
         <v>278</v>
       </c>
       <c r="C133">
@@ -9618,7 +9625,7 @@
       <c r="A134" t="s">
         <v>279</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="2" t="s">
         <v>280</v>
       </c>
       <c r="C134">
@@ -9662,17 +9669,17 @@
       <c r="A135" t="s">
         <v>281</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="2" t="s">
         <v>282</v>
       </c>
       <c r="C135">
         <v>150</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F135">
         <v>-1</v>
@@ -9706,17 +9713,17 @@
       <c r="A136" t="s">
         <v>283</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="2" t="s">
         <v>284</v>
       </c>
       <c r="C136">
         <v>150</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F136">
         <v>-1</v>
@@ -9750,7 +9757,7 @@
       <c r="A137" t="s">
         <v>285</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="2" t="s">
         <v>286</v>
       </c>
       <c r="C137">
@@ -9794,17 +9801,17 @@
       <c r="A138" t="s">
         <v>287</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="2" t="s">
         <v>288</v>
       </c>
       <c r="C138">
         <v>150</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F138">
         <v>-1</v>
@@ -9838,17 +9845,17 @@
       <c r="A139" t="s">
         <v>289</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="2" t="s">
         <v>290</v>
       </c>
       <c r="C139">
         <v>150</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F139">
         <v>-1</v>
@@ -9882,7 +9889,7 @@
       <c r="A140" t="s">
         <v>291</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="2" t="s">
         <v>292</v>
       </c>
       <c r="C140">
@@ -9926,7 +9933,7 @@
       <c r="A141" t="s">
         <v>293</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="2" t="s">
         <v>294</v>
       </c>
       <c r="C141">
@@ -9970,7 +9977,7 @@
       <c r="A142" t="s">
         <v>295</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="2" t="s">
         <v>296</v>
       </c>
       <c r="C142">
@@ -10014,7 +10021,7 @@
       <c r="A143" t="s">
         <v>297</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C143">
@@ -10058,7 +10065,7 @@
       <c r="A144" t="s">
         <v>299</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="2" t="s">
         <v>300</v>
       </c>
       <c r="C144">
@@ -10102,7 +10109,7 @@
       <c r="A145" t="s">
         <v>301</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="2" t="s">
         <v>302</v>
       </c>
       <c r="C145">
@@ -10146,7 +10153,7 @@
       <c r="A146" t="s">
         <v>303</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="2" t="s">
         <v>304</v>
       </c>
       <c r="C146">
@@ -10190,7 +10197,7 @@
       <c r="A147" t="s">
         <v>305</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C147">
@@ -10234,7 +10241,7 @@
       <c r="A148" t="s">
         <v>307</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="2" t="s">
         <v>308</v>
       </c>
       <c r="C148">
@@ -10278,7 +10285,7 @@
       <c r="A149" t="s">
         <v>309</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="2" t="s">
         <v>310</v>
       </c>
       <c r="C149">
@@ -10322,7 +10329,7 @@
       <c r="A150" t="s">
         <v>311</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="2" t="s">
         <v>312</v>
       </c>
       <c r="C150">
@@ -10366,7 +10373,7 @@
       <c r="A151" t="s">
         <v>313</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="2" t="s">
         <v>314</v>
       </c>
       <c r="C151">
@@ -10410,7 +10417,7 @@
       <c r="A152" t="s">
         <v>315</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="2" t="s">
         <v>316</v>
       </c>
       <c r="C152">
@@ -10454,7 +10461,7 @@
       <c r="A153" t="s">
         <v>317</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="2" t="s">
         <v>318</v>
       </c>
       <c r="C153">
@@ -10498,7 +10505,7 @@
       <c r="A154" t="s">
         <v>319</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="2" t="s">
         <v>320</v>
       </c>
       <c r="C154">
@@ -10542,7 +10549,7 @@
       <c r="A155" t="s">
         <v>321</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="2" t="s">
         <v>322</v>
       </c>
       <c r="C155">
@@ -10586,7 +10593,7 @@
       <c r="A156" t="s">
         <v>323</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="2" t="s">
         <v>324</v>
       </c>
       <c r="C156">
@@ -10630,7 +10637,7 @@
       <c r="A157" t="s">
         <v>325</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="2" t="s">
         <v>326</v>
       </c>
       <c r="C157">
@@ -10674,7 +10681,7 @@
       <c r="A158" t="s">
         <v>327</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="2" t="s">
         <v>328</v>
       </c>
       <c r="C158">
@@ -10718,7 +10725,7 @@
       <c r="A159" t="s">
         <v>329</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C159">
@@ -10762,7 +10769,7 @@
       <c r="A160" t="s">
         <v>331</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="2" t="s">
         <v>332</v>
       </c>
       <c r="C160">
@@ -10806,7 +10813,7 @@
       <c r="A161" t="s">
         <v>333</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="2" t="s">
         <v>334</v>
       </c>
       <c r="C161">
@@ -10850,7 +10857,7 @@
       <c r="A162" t="s">
         <v>335</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="2" t="s">
         <v>336</v>
       </c>
       <c r="C162">
@@ -10894,7 +10901,7 @@
       <c r="A163" t="s">
         <v>337</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="2" t="s">
         <v>338</v>
       </c>
       <c r="C163">
@@ -10938,7 +10945,7 @@
       <c r="A164" t="s">
         <v>339</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="2" t="s">
         <v>340</v>
       </c>
       <c r="C164">
@@ -10982,7 +10989,7 @@
       <c r="A165" t="s">
         <v>341</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="2" t="s">
         <v>342</v>
       </c>
       <c r="C165">
@@ -11026,7 +11033,7 @@
       <c r="A166" t="s">
         <v>343</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="2" t="s">
         <v>344</v>
       </c>
       <c r="C166">
@@ -11070,7 +11077,7 @@
       <c r="A167" t="s">
         <v>345</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="2" t="s">
         <v>346</v>
       </c>
       <c r="C167">
@@ -11114,7 +11121,7 @@
       <c r="A168" t="s">
         <v>347</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="2" t="s">
         <v>348</v>
       </c>
       <c r="C168">
@@ -11158,7 +11165,7 @@
       <c r="A169" t="s">
         <v>349</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="2" t="s">
         <v>350</v>
       </c>
       <c r="C169">
@@ -11202,7 +11209,7 @@
       <c r="A170" t="s">
         <v>351</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C170">
@@ -11246,7 +11253,7 @@
       <c r="A171" t="s">
         <v>353</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="2" t="s">
         <v>354</v>
       </c>
       <c r="C171">
@@ -11290,7 +11297,7 @@
       <c r="A172" t="s">
         <v>355</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C172">
@@ -11334,7 +11341,7 @@
       <c r="A173" t="s">
         <v>357</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="2" t="s">
         <v>358</v>
       </c>
       <c r="C173">
@@ -11378,7 +11385,7 @@
       <c r="A174" t="s">
         <v>359</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="2" t="s">
         <v>360</v>
       </c>
       <c r="C174">
@@ -11422,7 +11429,7 @@
       <c r="A175" t="s">
         <v>361</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="2" t="s">
         <v>362</v>
       </c>
       <c r="C175">
@@ -11466,7 +11473,7 @@
       <c r="A176" t="s">
         <v>363</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="2" t="s">
         <v>364</v>
       </c>
       <c r="C176">
@@ -11510,7 +11517,7 @@
       <c r="A177" t="s">
         <v>365</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="2" t="s">
         <v>366</v>
       </c>
       <c r="C177">
@@ -11554,7 +11561,7 @@
       <c r="A178" t="s">
         <v>367</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="2" t="s">
         <v>368</v>
       </c>
       <c r="C178">
@@ -11598,7 +11605,7 @@
       <c r="A179" t="s">
         <v>369</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C179">
@@ -11642,7 +11649,7 @@
       <c r="A180" t="s">
         <v>370</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="2" t="s">
         <v>371</v>
       </c>
       <c r="C180">
@@ -11686,7 +11693,7 @@
       <c r="A181" t="s">
         <v>372</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="2" t="s">
         <v>373</v>
       </c>
       <c r="C181">
@@ -11730,7 +11737,7 @@
       <c r="A182" t="s">
         <v>374</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="2" t="s">
         <v>375</v>
       </c>
       <c r="C182">
@@ -11774,7 +11781,7 @@
       <c r="A183" t="s">
         <v>376</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="2" t="s">
         <v>377</v>
       </c>
       <c r="C183">
@@ -11818,7 +11825,7 @@
       <c r="A184" t="s">
         <v>378</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="2" t="s">
         <v>379</v>
       </c>
       <c r="C184">
@@ -11862,7 +11869,7 @@
       <c r="A185" t="s">
         <v>380</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="2" t="s">
         <v>381</v>
       </c>
       <c r="C185">
@@ -11906,7 +11913,7 @@
       <c r="A186" t="s">
         <v>382</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="2" t="s">
         <v>383</v>
       </c>
       <c r="C186">
@@ -11950,7 +11957,7 @@
       <c r="A187" t="s">
         <v>384</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C187">
@@ -11994,7 +12001,7 @@
       <c r="A188" t="s">
         <v>386</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="2" t="s">
         <v>387</v>
       </c>
       <c r="C188">
@@ -12038,7 +12045,7 @@
       <c r="A189" t="s">
         <v>388</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="2" t="s">
         <v>389</v>
       </c>
       <c r="C189">
@@ -12082,7 +12089,7 @@
       <c r="A190" t="s">
         <v>390</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C190">
@@ -12126,7 +12133,7 @@
       <c r="A191" t="s">
         <v>392</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="2" t="s">
         <v>393</v>
       </c>
       <c r="C191">
@@ -12170,7 +12177,7 @@
       <c r="A192" t="s">
         <v>394</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="2" t="s">
         <v>395</v>
       </c>
       <c r="C192">
@@ -12214,7 +12221,7 @@
       <c r="A193" t="s">
         <v>396</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C193">
@@ -12258,7 +12265,7 @@
       <c r="A194" t="s">
         <v>398</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="2" t="s">
         <v>399</v>
       </c>
       <c r="C194">
@@ -12302,7 +12309,7 @@
       <c r="A195" t="s">
         <v>400</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="2" t="s">
         <v>401</v>
       </c>
       <c r="C195">
@@ -12346,7 +12353,7 @@
       <c r="A196" t="s">
         <v>402</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="2" t="s">
         <v>403</v>
       </c>
       <c r="C196">
@@ -12390,7 +12397,7 @@
       <c r="A197" t="s">
         <v>404</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="2" t="s">
         <v>405</v>
       </c>
       <c r="C197">
@@ -12434,7 +12441,7 @@
       <c r="A198" t="s">
         <v>406</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="2" t="s">
         <v>407</v>
       </c>
       <c r="C198">
@@ -12478,7 +12485,7 @@
       <c r="A199" t="s">
         <v>408</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="2" t="s">
         <v>409</v>
       </c>
       <c r="C199">
@@ -12522,7 +12529,7 @@
       <c r="A200" t="s">
         <v>410</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="2" t="s">
         <v>411</v>
       </c>
       <c r="C200">
@@ -12566,7 +12573,7 @@
       <c r="A201" t="s">
         <v>412</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="2" t="s">
         <v>413</v>
       </c>
       <c r="C201">
@@ -12610,7 +12617,7 @@
       <c r="A202" t="s">
         <v>414</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="2" t="s">
         <v>415</v>
       </c>
       <c r="C202">
@@ -12654,7 +12661,7 @@
       <c r="A203" t="s">
         <v>416</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="2" t="s">
         <v>417</v>
       </c>
       <c r="C203">
@@ -12698,7 +12705,7 @@
       <c r="A204" t="s">
         <v>418</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="2" t="s">
         <v>419</v>
       </c>
       <c r="C204">
@@ -12742,7 +12749,7 @@
       <c r="A205" t="s">
         <v>420</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C205">
@@ -12786,7 +12793,7 @@
       <c r="A206" t="s">
         <v>421</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="2" t="s">
         <v>422</v>
       </c>
       <c r="C206">
@@ -12830,17 +12837,17 @@
       <c r="A207" t="s">
         <v>423</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="2" t="s">
         <v>424</v>
       </c>
       <c r="C207">
         <v>1100</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F207">
         <v>-1</v>
@@ -12874,7 +12881,7 @@
       <c r="A208" t="s">
         <v>425</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="2" t="s">
         <v>426</v>
       </c>
       <c r="C208">
@@ -12918,7 +12925,7 @@
       <c r="A209" t="s">
         <v>427</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C209">
@@ -12962,17 +12969,17 @@
       <c r="A210" t="s">
         <v>428</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="2" t="s">
         <v>429</v>
       </c>
       <c r="C210">
         <v>900</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F210">
         <v>-1</v>
@@ -13006,7 +13013,7 @@
       <c r="A211" t="s">
         <v>430</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="2" t="s">
         <v>431</v>
       </c>
       <c r="C211">
@@ -13050,7 +13057,7 @@
       <c r="A212" t="s">
         <v>432</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="2" t="s">
         <v>433</v>
       </c>
       <c r="C212">
@@ -13094,7 +13101,7 @@
       <c r="A213" t="s">
         <v>434</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="2" t="s">
         <v>435</v>
       </c>
       <c r="C213">
@@ -13138,7 +13145,7 @@
       <c r="A214" t="s">
         <v>436</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="2" t="s">
         <v>437</v>
       </c>
       <c r="C214">
@@ -13182,7 +13189,7 @@
       <c r="A215" t="s">
         <v>438</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="2" t="s">
         <v>439</v>
       </c>
       <c r="C215">
@@ -13226,7 +13233,7 @@
       <c r="A216" t="s">
         <v>440</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="2" t="s">
         <v>441</v>
       </c>
       <c r="C216">
@@ -13270,7 +13277,7 @@
       <c r="A217" t="s">
         <v>442</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="2" t="s">
         <v>443</v>
       </c>
       <c r="C217">
@@ -13314,7 +13321,7 @@
       <c r="A218" t="s">
         <v>444</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="2" t="s">
         <v>445</v>
       </c>
       <c r="C218">
@@ -13358,7 +13365,7 @@
       <c r="A219" t="s">
         <v>446</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="2" t="s">
         <v>447</v>
       </c>
       <c r="C219">
@@ -13402,7 +13409,7 @@
       <c r="A220" t="s">
         <v>448</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="2" t="s">
         <v>449</v>
       </c>
       <c r="C220">
@@ -13446,7 +13453,7 @@
       <c r="A221" t="s">
         <v>450</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="2" t="s">
         <v>451</v>
       </c>
       <c r="C221">
@@ -13490,7 +13497,7 @@
       <c r="A222" t="s">
         <v>452</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="2" t="s">
         <v>453</v>
       </c>
       <c r="C222">
@@ -13534,7 +13541,7 @@
       <c r="A223" t="s">
         <v>454</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="2" t="s">
         <v>455</v>
       </c>
       <c r="C223">
@@ -13578,7 +13585,7 @@
       <c r="A224" t="s">
         <v>456</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="2" t="s">
         <v>457</v>
       </c>
       <c r="C224">
@@ -13622,7 +13629,7 @@
       <c r="A225" t="s">
         <v>458</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="2" t="s">
         <v>459</v>
       </c>
       <c r="C225">
@@ -13666,7 +13673,7 @@
       <c r="A226" t="s">
         <v>460</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="2" t="s">
         <v>461</v>
       </c>
       <c r="C226">
@@ -13710,7 +13717,7 @@
       <c r="A227" t="s">
         <v>462</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="2" t="s">
         <v>463</v>
       </c>
       <c r="C227">
@@ -13754,7 +13761,7 @@
       <c r="A228" t="s">
         <v>464</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="2" t="s">
         <v>465</v>
       </c>
       <c r="C228">
@@ -13798,7 +13805,7 @@
       <c r="A229" t="s">
         <v>466</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="2" t="s">
         <v>467</v>
       </c>
       <c r="C229">
@@ -13842,7 +13849,7 @@
       <c r="A230" t="s">
         <v>468</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="2" t="s">
         <v>469</v>
       </c>
       <c r="C230">
@@ -13886,7 +13893,7 @@
       <c r="A231" t="s">
         <v>470</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="2" t="s">
         <v>471</v>
       </c>
       <c r="C231">
@@ -13930,7 +13937,7 @@
       <c r="A232" t="s">
         <v>472</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="2" t="s">
         <v>473</v>
       </c>
       <c r="C232">
@@ -13974,17 +13981,17 @@
       <c r="A233" t="s">
         <v>474</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="2" t="s">
         <v>475</v>
       </c>
       <c r="C233">
         <v>300</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>476</v>
+        <v>210</v>
       </c>
       <c r="F233">
         <v>-1</v>
@@ -14018,17 +14025,17 @@
       <c r="A234" t="s">
         <v>477</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="2" t="s">
         <v>478</v>
       </c>
       <c r="C234">
         <v>500</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F234">
         <v>-1</v>
@@ -14062,17 +14069,17 @@
       <c r="A235" t="s">
         <v>479</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="2" t="s">
         <v>480</v>
       </c>
       <c r="C235">
         <v>500</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>476</v>
+        <v>210</v>
       </c>
       <c r="F235">
         <v>-1</v>
@@ -14106,7 +14113,7 @@
       <c r="A236" t="s">
         <v>481</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="2" t="s">
         <v>482</v>
       </c>
       <c r="C236">
@@ -14150,17 +14157,17 @@
       <c r="A237" t="s">
         <v>483</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="2" t="s">
         <v>484</v>
       </c>
       <c r="C237">
         <v>800</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F237">
         <v>-1</v>
@@ -14194,7 +14201,7 @@
       <c r="A238" t="s">
         <v>485</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="2" t="s">
         <v>486</v>
       </c>
       <c r="C238">
@@ -14238,17 +14245,17 @@
       <c r="A239" t="s">
         <v>487</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="2" t="s">
         <v>488</v>
       </c>
       <c r="C239">
         <v>450</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F239">
         <v>-1</v>
@@ -14282,17 +14289,17 @@
       <c r="A240" t="s">
         <v>489</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" s="2" t="s">
         <v>490</v>
       </c>
       <c r="C240">
         <v>350</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F240">
         <v>-1</v>
@@ -14326,17 +14333,17 @@
       <c r="A241" t="s">
         <v>491</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C241">
         <v>250</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F241">
         <v>-1</v>
@@ -14370,7 +14377,7 @@
       <c r="A242" t="s">
         <v>493</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" s="2" t="s">
         <v>494</v>
       </c>
       <c r="C242">
@@ -14414,17 +14421,17 @@
       <c r="A243" t="s">
         <v>495</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" s="2" t="s">
         <v>496</v>
       </c>
       <c r="C243">
         <v>700</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F243">
         <v>-1</v>
@@ -14458,17 +14465,17 @@
       <c r="A244" t="s">
         <v>497</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" s="2" t="s">
         <v>498</v>
       </c>
       <c r="C244">
         <v>800</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F244">
         <v>-1</v>
@@ -14502,7 +14509,7 @@
       <c r="A245" t="s">
         <v>499</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="2" t="s">
         <v>500</v>
       </c>
       <c r="C245">
@@ -14546,7 +14553,7 @@
       <c r="A246" t="s">
         <v>502</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="2" t="s">
         <v>503</v>
       </c>
       <c r="C246">
@@ -14590,7 +14597,7 @@
       <c r="A247" t="s">
         <v>504</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="2" t="s">
         <v>505</v>
       </c>
       <c r="C247">
@@ -14634,7 +14641,7 @@
       <c r="A248" t="s">
         <v>506</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="2" t="s">
         <v>507</v>
       </c>
       <c r="C248">
@@ -14678,7 +14685,7 @@
       <c r="A249" t="s">
         <v>508</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="2" t="s">
         <v>509</v>
       </c>
       <c r="C249">
@@ -14722,7 +14729,7 @@
       <c r="A250" t="s">
         <v>510</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="2" t="s">
         <v>511</v>
       </c>
       <c r="C250">
@@ -14766,7 +14773,7 @@
       <c r="A251" t="s">
         <v>512</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="2" t="s">
         <v>513</v>
       </c>
       <c r="C251">
@@ -14810,7 +14817,7 @@
       <c r="A252" t="s">
         <v>514</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="2" t="s">
         <v>515</v>
       </c>
       <c r="C252">
@@ -14854,7 +14861,7 @@
       <c r="A253" t="s">
         <v>516</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="2" t="s">
         <v>517</v>
       </c>
       <c r="C253">
@@ -14898,7 +14905,7 @@
       <c r="A254" t="s">
         <v>518</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="2" t="s">
         <v>519</v>
       </c>
       <c r="C254">
@@ -14942,7 +14949,7 @@
       <c r="A255" t="s">
         <v>520</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="2" t="s">
         <v>521</v>
       </c>
       <c r="C255">
@@ -14986,7 +14993,7 @@
       <c r="A256" t="s">
         <v>522</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="2" t="s">
         <v>523</v>
       </c>
       <c r="C256">
@@ -15030,7 +15037,7 @@
       <c r="A257" t="s">
         <v>524</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="2" t="s">
         <v>525</v>
       </c>
       <c r="C257">
@@ -15074,7 +15081,7 @@
       <c r="A258" t="s">
         <v>526</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="2" t="s">
         <v>527</v>
       </c>
       <c r="C258">
@@ -15118,7 +15125,7 @@
       <c r="A259" t="s">
         <v>529</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="2" t="s">
         <v>530</v>
       </c>
       <c r="C259">
@@ -15162,7 +15169,7 @@
       <c r="A260" t="s">
         <v>531</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="2" t="s">
         <v>532</v>
       </c>
       <c r="C260">
@@ -15206,7 +15213,7 @@
       <c r="A261" t="s">
         <v>533</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="2" t="s">
         <v>534</v>
       </c>
       <c r="C261">
@@ -15250,7 +15257,7 @@
       <c r="A262" t="s">
         <v>535</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="2" t="s">
         <v>536</v>
       </c>
       <c r="C262">
@@ -15294,7 +15301,7 @@
       <c r="A263" t="s">
         <v>537</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="2" t="s">
         <v>538</v>
       </c>
       <c r="C263">
@@ -15338,7 +15345,7 @@
       <c r="A264" t="s">
         <v>539</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="2" t="s">
         <v>540</v>
       </c>
       <c r="C264">
@@ -15382,7 +15389,7 @@
       <c r="A265" t="s">
         <v>541</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="2" t="s">
         <v>542</v>
       </c>
       <c r="C265">
@@ -15426,7 +15433,7 @@
       <c r="A266" t="s">
         <v>543</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="2" t="s">
         <v>544</v>
       </c>
       <c r="C266">
@@ -15470,7 +15477,7 @@
       <c r="A267" t="s">
         <v>545</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="2" t="s">
         <v>546</v>
       </c>
       <c r="C267">
@@ -15514,7 +15521,7 @@
       <c r="A268" t="s">
         <v>548</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="2" t="s">
         <v>549</v>
       </c>
       <c r="C268">
@@ -15558,7 +15565,7 @@
       <c r="A269" t="s">
         <v>550</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C269">
@@ -15602,7 +15609,7 @@
       <c r="A270" t="s">
         <v>552</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="2" t="s">
         <v>553</v>
       </c>
       <c r="C270">
@@ -15646,7 +15653,7 @@
       <c r="A271" t="s">
         <v>554</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" s="2" t="s">
         <v>555</v>
       </c>
       <c r="C271">
@@ -15690,7 +15697,7 @@
       <c r="A272" t="s">
         <v>556</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" s="2" t="s">
         <v>557</v>
       </c>
       <c r="C272">
@@ -15734,7 +15741,7 @@
       <c r="A273" t="s">
         <v>558</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" s="2" t="s">
         <v>559</v>
       </c>
       <c r="C273">
@@ -15778,7 +15785,7 @@
       <c r="A274" t="s">
         <v>560</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" s="2" t="s">
         <v>561</v>
       </c>
       <c r="C274">
@@ -15822,7 +15829,7 @@
       <c r="A275" t="s">
         <v>562</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" s="2" t="s">
         <v>563</v>
       </c>
       <c r="C275">
@@ -15866,7 +15873,7 @@
       <c r="A276" t="s">
         <v>564</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" s="2" t="s">
         <v>565</v>
       </c>
       <c r="C276">
@@ -15910,7 +15917,7 @@
       <c r="A277" t="s">
         <v>566</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" s="2" t="s">
         <v>567</v>
       </c>
       <c r="C277">
@@ -15954,7 +15961,7 @@
       <c r="A278" t="s">
         <v>568</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="2" t="s">
         <v>569</v>
       </c>
       <c r="C278">
@@ -15998,7 +16005,7 @@
       <c r="A279" t="s">
         <v>570</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="2" t="s">
         <v>571</v>
       </c>
       <c r="C279">
@@ -16042,7 +16049,7 @@
       <c r="A280" t="s">
         <v>572</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" s="2" t="s">
         <v>573</v>
       </c>
       <c r="C280">
@@ -16086,7 +16093,7 @@
       <c r="A281" t="s">
         <v>574</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="2" t="s">
         <v>575</v>
       </c>
       <c r="C281">
@@ -16130,7 +16137,7 @@
       <c r="A282" t="s">
         <v>576</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="2" t="s">
         <v>577</v>
       </c>
       <c r="C282">
@@ -16174,7 +16181,7 @@
       <c r="A283" t="s">
         <v>578</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" s="2" t="s">
         <v>579</v>
       </c>
       <c r="C283">
@@ -16218,7 +16225,7 @@
       <c r="A284" t="s">
         <v>580</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="2" t="s">
         <v>581</v>
       </c>
       <c r="C284">
@@ -16262,7 +16269,7 @@
       <c r="A285" t="s">
         <v>582</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" s="2" t="s">
         <v>583</v>
       </c>
       <c r="C285">
@@ -16306,7 +16313,7 @@
       <c r="A286" t="s">
         <v>584</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="2" t="s">
         <v>585</v>
       </c>
       <c r="C286">
@@ -16350,7 +16357,7 @@
       <c r="A287" t="s">
         <v>586</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" s="2" t="s">
         <v>587</v>
       </c>
       <c r="C287">
@@ -16394,7 +16401,7 @@
       <c r="A288" t="s">
         <v>588</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" s="2" t="s">
         <v>589</v>
       </c>
       <c r="C288">
@@ -16438,7 +16445,7 @@
       <c r="A289" t="s">
         <v>590</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" s="2" t="s">
         <v>591</v>
       </c>
       <c r="C289">
@@ -16482,7 +16489,7 @@
       <c r="A290" t="s">
         <v>592</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" s="2" t="s">
         <v>593</v>
       </c>
       <c r="C290">
@@ -16526,7 +16533,7 @@
       <c r="A291" t="s">
         <v>594</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" s="2" t="s">
         <v>595</v>
       </c>
       <c r="C291">
@@ -16570,7 +16577,7 @@
       <c r="A292" t="s">
         <v>596</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" s="2" t="s">
         <v>597</v>
       </c>
       <c r="C292">
@@ -16614,7 +16621,7 @@
       <c r="A293" t="s">
         <v>598</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" s="2" t="s">
         <v>599</v>
       </c>
       <c r="C293">
@@ -16658,7 +16665,7 @@
       <c r="A294" t="s">
         <v>600</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B294" s="2" t="s">
         <v>601</v>
       </c>
       <c r="C294">
@@ -16702,7 +16709,7 @@
       <c r="A295" t="s">
         <v>602</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B295" s="2" t="s">
         <v>603</v>
       </c>
       <c r="C295">
@@ -16746,7 +16753,7 @@
       <c r="A296" t="s">
         <v>604</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B296" s="2" t="s">
         <v>605</v>
       </c>
       <c r="C296">
@@ -16790,17 +16797,17 @@
       <c r="A297" t="s">
         <v>606</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B297" s="2" t="s">
         <v>607</v>
       </c>
       <c r="C297">
         <v>7500</v>
       </c>
       <c r="D297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F297">
         <v>-1</v>
@@ -16834,7 +16841,7 @@
       <c r="A298" t="s">
         <v>608</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B298" s="2" t="s">
         <v>609</v>
       </c>
       <c r="C298">
@@ -16878,17 +16885,17 @@
       <c r="A299" t="s">
         <v>610</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B299" s="2" t="s">
         <v>611</v>
       </c>
       <c r="C299">
         <v>14900</v>
       </c>
       <c r="D299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F299">
         <v>-1</v>
@@ -16922,17 +16929,17 @@
       <c r="A300" t="s">
         <v>612</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B300" s="2" t="s">
         <v>613</v>
       </c>
       <c r="C300">
         <v>6500</v>
       </c>
       <c r="D300">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F300">
         <v>-1</v>
@@ -16966,17 +16973,17 @@
       <c r="A301" t="s">
         <v>614</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B301" s="2" t="s">
         <v>615</v>
       </c>
       <c r="C301">
         <v>4900</v>
       </c>
       <c r="D301">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F301">
         <v>-1</v>
@@ -17010,17 +17017,17 @@
       <c r="A302" t="s">
         <v>616</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B302" s="2" t="s">
         <v>617</v>
       </c>
       <c r="C302">
         <v>2400</v>
       </c>
       <c r="D302">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F302">
         <v>-1</v>
@@ -17054,17 +17061,17 @@
       <c r="A303" t="s">
         <v>618</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B303" s="2" t="s">
         <v>619</v>
       </c>
       <c r="C303">
         <v>1500</v>
       </c>
       <c r="D303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F303">
         <v>-1</v>
@@ -17098,17 +17105,17 @@
       <c r="A304" t="s">
         <v>620</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B304" s="2" t="s">
         <v>621</v>
       </c>
       <c r="C304">
         <v>8900</v>
       </c>
       <c r="D304">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F304">
         <v>-1</v>
@@ -17142,17 +17149,17 @@
       <c r="A305" t="s">
         <v>622</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B305" s="2" t="s">
         <v>623</v>
       </c>
       <c r="C305">
         <v>5900</v>
       </c>
       <c r="D305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F305">
         <v>-1</v>
@@ -17186,17 +17193,17 @@
       <c r="A306" t="s">
         <v>624</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B306" s="2" t="s">
         <v>625</v>
       </c>
       <c r="C306">
         <v>4400</v>
       </c>
       <c r="D306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F306">
         <v>-1</v>
@@ -17230,17 +17237,17 @@
       <c r="A307" t="s">
         <v>626</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B307" s="2" t="s">
         <v>627</v>
       </c>
       <c r="C307">
         <v>1100</v>
       </c>
       <c r="D307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F307">
         <v>-1</v>
@@ -17274,17 +17281,17 @@
       <c r="A308" t="s">
         <v>628</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B308" s="2" t="s">
         <v>629</v>
       </c>
       <c r="C308">
         <v>7800</v>
       </c>
       <c r="D308">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F308">
         <v>-1</v>
@@ -17318,17 +17325,17 @@
       <c r="A309" t="s">
         <v>630</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B309" s="2" t="s">
         <v>631</v>
       </c>
       <c r="C309">
         <v>6800</v>
       </c>
       <c r="D309">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F309">
         <v>-1</v>
@@ -17362,17 +17369,17 @@
       <c r="A310" t="s">
         <v>632</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B310" s="2" t="s">
         <v>633</v>
       </c>
       <c r="C310">
         <v>7500</v>
       </c>
       <c r="D310">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F310">
         <v>-1</v>
@@ -17406,7 +17413,7 @@
       <c r="A311" t="s">
         <v>634</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B311" s="2" t="s">
         <v>635</v>
       </c>
       <c r="C311">
@@ -17450,17 +17457,17 @@
       <c r="A312" t="s">
         <v>636</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B312" s="2" t="s">
         <v>637</v>
       </c>
       <c r="C312">
         <v>2600</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F312">
         <v>-1</v>
@@ -17494,17 +17501,17 @@
       <c r="A313" t="s">
         <v>638</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B313" s="2" t="s">
         <v>639</v>
       </c>
       <c r="C313">
         <v>1300</v>
       </c>
       <c r="D313">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F313">
         <v>-1</v>
@@ -17538,7 +17545,7 @@
       <c r="A314" t="s">
         <v>640</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B314" s="2" t="s">
         <v>641</v>
       </c>
       <c r="C314">
@@ -17582,7 +17589,7 @@
       <c r="A315" t="s">
         <v>642</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B315" s="2" t="s">
         <v>643</v>
       </c>
       <c r="C315">
@@ -17626,7 +17633,7 @@
       <c r="A316" t="s">
         <v>644</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B316" s="2" t="s">
         <v>645</v>
       </c>
       <c r="C316">
@@ -17670,7 +17677,7 @@
       <c r="A317" t="s">
         <v>646</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B317" s="2" t="s">
         <v>647</v>
       </c>
       <c r="C317">
@@ -17714,7 +17721,7 @@
       <c r="A318" t="s">
         <v>648</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B318" s="2" t="s">
         <v>649</v>
       </c>
       <c r="C318">
@@ -17758,7 +17765,7 @@
       <c r="A319" t="s">
         <v>650</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B319" s="2" t="s">
         <v>651</v>
       </c>
       <c r="C319">
@@ -17802,7 +17809,7 @@
       <c r="A320" t="s">
         <v>652</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="2" t="s">
         <v>653</v>
       </c>
       <c r="C320">
@@ -17846,7 +17853,7 @@
       <c r="A321" t="s">
         <v>654</v>
       </c>
-      <c r="B321" t="s">
+      <c r="B321" s="2" t="s">
         <v>655</v>
       </c>
       <c r="C321">
@@ -17890,7 +17897,7 @@
       <c r="A322" t="s">
         <v>656</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B322" s="2" t="s">
         <v>657</v>
       </c>
       <c r="C322">
@@ -17934,7 +17941,7 @@
       <c r="A323" t="s">
         <v>658</v>
       </c>
-      <c r="B323" t="s">
+      <c r="B323" s="2" t="s">
         <v>659</v>
       </c>
       <c r="C323">
@@ -17978,7 +17985,7 @@
       <c r="A324" t="s">
         <v>660</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B324" s="2" t="s">
         <v>661</v>
       </c>
       <c r="C324">
@@ -18022,7 +18029,7 @@
       <c r="A325" t="s">
         <v>662</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B325" s="2" t="s">
         <v>663</v>
       </c>
       <c r="C325">
@@ -18066,7 +18073,7 @@
       <c r="A326" t="s">
         <v>664</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B326" s="2" t="s">
         <v>665</v>
       </c>
       <c r="C326">
@@ -18110,7 +18117,7 @@
       <c r="A327" t="s">
         <v>666</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B327" s="2" t="s">
         <v>667</v>
       </c>
       <c r="C327">
@@ -18154,7 +18161,7 @@
       <c r="A328" t="s">
         <v>668</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B328" s="2" t="s">
         <v>669</v>
       </c>
       <c r="C328">
@@ -18198,7 +18205,7 @@
       <c r="A329" t="s">
         <v>670</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B329" s="2" t="s">
         <v>671</v>
       </c>
       <c r="C329">
@@ -18242,7 +18249,7 @@
       <c r="A330" t="s">
         <v>672</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B330" s="2" t="s">
         <v>673</v>
       </c>
       <c r="C330">
@@ -18286,7 +18293,7 @@
       <c r="A331" t="s">
         <v>674</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B331" s="2" t="s">
         <v>675</v>
       </c>
       <c r="C331">
@@ -18330,7 +18337,7 @@
       <c r="A332" t="s">
         <v>676</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B332" s="2" t="s">
         <v>677</v>
       </c>
       <c r="C332">
@@ -18374,7 +18381,7 @@
       <c r="A333" t="s">
         <v>678</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B333" s="2" t="s">
         <v>679</v>
       </c>
       <c r="C333">
@@ -18418,7 +18425,7 @@
       <c r="A334" t="s">
         <v>680</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="2" t="s">
         <v>681</v>
       </c>
       <c r="C334">
@@ -18462,7 +18469,7 @@
       <c r="A335" t="s">
         <v>682</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="2" t="s">
         <v>683</v>
       </c>
       <c r="C335">
@@ -18506,17 +18513,17 @@
       <c r="A336" t="s">
         <v>684</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="2" t="s">
         <v>685</v>
       </c>
       <c r="C336">
         <v>65500</v>
       </c>
       <c r="D336">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F336">
         <v>-1</v>
@@ -18550,7 +18557,7 @@
       <c r="A337" t="s">
         <v>686</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B337" s="2" t="s">
         <v>687</v>
       </c>
       <c r="C337">
@@ -18594,7 +18601,7 @@
       <c r="A338" t="s">
         <v>688</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B338" s="2" t="s">
         <v>689</v>
       </c>
       <c r="C338">
@@ -18638,17 +18645,17 @@
       <c r="A339" t="s">
         <v>690</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="2" t="s">
         <v>691</v>
       </c>
       <c r="C339">
         <v>63000</v>
       </c>
       <c r="D339">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F339">
         <v>-1</v>
@@ -18682,7 +18689,7 @@
       <c r="A340" t="s">
         <v>692</v>
       </c>
-      <c r="B340" t="s">
+      <c r="B340" s="2" t="s">
         <v>693</v>
       </c>
       <c r="C340">
@@ -18726,7 +18733,7 @@
       <c r="A341" t="s">
         <v>694</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B341" s="2" t="s">
         <v>695</v>
       </c>
       <c r="C341">
@@ -18770,17 +18777,17 @@
       <c r="A342" t="s">
         <v>696</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B342" s="2" t="s">
         <v>697</v>
       </c>
       <c r="C342">
         <v>63000</v>
       </c>
       <c r="D342">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F342">
         <v>-1</v>
@@ -18814,7 +18821,7 @@
       <c r="A343" t="s">
         <v>698</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B343" s="2" t="s">
         <v>699</v>
       </c>
       <c r="C343">
@@ -18858,7 +18865,7 @@
       <c r="A344" t="s">
         <v>700</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B344" s="2" t="s">
         <v>701</v>
       </c>
       <c r="C344">
@@ -18902,17 +18909,17 @@
       <c r="A345" t="s">
         <v>702</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B345" s="2" t="s">
         <v>703</v>
       </c>
       <c r="C345">
         <v>57000</v>
       </c>
       <c r="D345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F345">
         <v>-1</v>
@@ -18946,7 +18953,7 @@
       <c r="A346" t="s">
         <v>704</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B346" s="2" t="s">
         <v>705</v>
       </c>
       <c r="C346">
@@ -18990,7 +18997,7 @@
       <c r="A347" t="s">
         <v>706</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B347" s="2" t="s">
         <v>707</v>
       </c>
       <c r="C347">
@@ -19034,17 +19041,17 @@
       <c r="A348" t="s">
         <v>708</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B348" s="2" t="s">
         <v>709</v>
       </c>
       <c r="C348">
         <v>60000</v>
       </c>
       <c r="D348">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F348">
         <v>-1</v>
@@ -19078,7 +19085,7 @@
       <c r="A349" t="s">
         <v>710</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B349" s="2" t="s">
         <v>711</v>
       </c>
       <c r="C349">
@@ -19122,7 +19129,7 @@
       <c r="A350" t="s">
         <v>712</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B350" s="2" t="s">
         <v>713</v>
       </c>
       <c r="C350">
@@ -19166,17 +19173,17 @@
       <c r="A351" t="s">
         <v>714</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B351" s="2" t="s">
         <v>715</v>
       </c>
       <c r="C351">
         <v>48000</v>
       </c>
       <c r="D351">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F351">
         <v>-1</v>
@@ -19210,7 +19217,7 @@
       <c r="A352" t="s">
         <v>716</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="2" t="s">
         <v>717</v>
       </c>
       <c r="C352">
@@ -19254,7 +19261,7 @@
       <c r="A353" t="s">
         <v>718</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B353" s="2" t="s">
         <v>719</v>
       </c>
       <c r="C353">
@@ -19298,17 +19305,17 @@
       <c r="A354" t="s">
         <v>720</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B354" s="2" t="s">
         <v>721</v>
       </c>
       <c r="C354">
         <v>41000</v>
       </c>
       <c r="D354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F354">
         <v>-1</v>
@@ -19342,7 +19349,7 @@
       <c r="A355" t="s">
         <v>722</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B355" s="2" t="s">
         <v>723</v>
       </c>
       <c r="C355">
@@ -19386,7 +19393,7 @@
       <c r="A356" t="s">
         <v>724</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B356" s="2" t="s">
         <v>725</v>
       </c>
       <c r="C356">
@@ -19430,17 +19437,17 @@
       <c r="A357" t="s">
         <v>726</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B357" s="2" t="s">
         <v>727</v>
       </c>
       <c r="C357">
         <v>41000</v>
       </c>
       <c r="D357">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F357">
         <v>-1</v>
@@ -19474,7 +19481,7 @@
       <c r="A358" t="s">
         <v>728</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B358" s="2" t="s">
         <v>729</v>
       </c>
       <c r="C358">
@@ -19518,7 +19525,7 @@
       <c r="A359" t="s">
         <v>730</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B359" s="2" t="s">
         <v>731</v>
       </c>
       <c r="C359">
@@ -19562,17 +19569,17 @@
       <c r="A360" t="s">
         <v>732</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B360" s="2" t="s">
         <v>733</v>
       </c>
       <c r="C360">
         <v>41000</v>
       </c>
       <c r="D360">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F360">
         <v>-1</v>
@@ -19606,7 +19613,7 @@
       <c r="A361" t="s">
         <v>734</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B361" s="2" t="s">
         <v>735</v>
       </c>
       <c r="C361">
@@ -19650,7 +19657,7 @@
       <c r="A362" t="s">
         <v>736</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B362" s="2" t="s">
         <v>737</v>
       </c>
       <c r="C362">
@@ -19694,17 +19701,17 @@
       <c r="A363" t="s">
         <v>738</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B363" s="2" t="s">
         <v>739</v>
       </c>
       <c r="C363">
         <v>38000</v>
       </c>
       <c r="D363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F363">
         <v>-1</v>
@@ -19738,7 +19745,7 @@
       <c r="A364" t="s">
         <v>740</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B364" s="2" t="s">
         <v>741</v>
       </c>
       <c r="C364">
@@ -19782,7 +19789,7 @@
       <c r="A365" t="s">
         <v>742</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B365" s="2" t="s">
         <v>743</v>
       </c>
       <c r="C365">
@@ -19826,17 +19833,17 @@
       <c r="A366" t="s">
         <v>744</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B366" s="2" t="s">
         <v>745</v>
       </c>
       <c r="C366">
         <v>38000</v>
       </c>
       <c r="D366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F366">
         <v>-1</v>
@@ -19870,7 +19877,7 @@
       <c r="A367" t="s">
         <v>746</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="2" t="s">
         <v>747</v>
       </c>
       <c r="C367">
@@ -19914,17 +19921,17 @@
       <c r="A368" t="s">
         <v>748</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="2" t="s">
         <v>749</v>
       </c>
       <c r="C368">
         <v>41000</v>
       </c>
       <c r="D368">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F368">
         <v>-1</v>
@@ -19958,17 +19965,17 @@
       <c r="A369" t="s">
         <v>750</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B369" s="2" t="s">
         <v>751</v>
       </c>
       <c r="C369">
         <v>41000</v>
       </c>
       <c r="D369">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F369">
         <v>-1</v>
@@ -20002,7 +20009,7 @@
       <c r="A370" t="s">
         <v>752</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B370" s="2" t="s">
         <v>753</v>
       </c>
       <c r="C370">
@@ -20046,17 +20053,17 @@
       <c r="A371" t="s">
         <v>754</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B371" s="2" t="s">
         <v>755</v>
       </c>
       <c r="C371">
         <v>32500</v>
       </c>
       <c r="D371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F371">
         <v>-1</v>
@@ -20090,17 +20097,17 @@
       <c r="A372" t="s">
         <v>756</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B372" s="2" t="s">
         <v>757</v>
       </c>
       <c r="C372">
         <v>19500</v>
       </c>
       <c r="D372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F372">
         <v>-1</v>
@@ -20134,17 +20141,17 @@
       <c r="A373" t="s">
         <v>758</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B373" s="2" t="s">
         <v>759</v>
       </c>
       <c r="C373">
         <v>9750</v>
       </c>
       <c r="D373">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F373">
         <v>-1</v>
@@ -20178,17 +20185,17 @@
       <c r="A374" t="s">
         <v>760</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B374" s="2" t="s">
         <v>761</v>
       </c>
       <c r="C374">
         <v>32500</v>
       </c>
       <c r="D374">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F374">
         <v>-1</v>
@@ -20222,17 +20229,17 @@
       <c r="A375" t="s">
         <v>762</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B375" s="2" t="s">
         <v>763</v>
       </c>
       <c r="C375">
         <v>19500</v>
       </c>
       <c r="D375">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F375">
         <v>-1</v>
@@ -20266,17 +20273,17 @@
       <c r="A376" t="s">
         <v>764</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B376" s="2" t="s">
         <v>765</v>
       </c>
       <c r="C376">
         <v>9750</v>
       </c>
       <c r="D376">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F376">
         <v>-1</v>
@@ -20310,7 +20317,7 @@
       <c r="A377" t="s">
         <v>766</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B377" s="2" t="s">
         <v>767</v>
       </c>
       <c r="C377">
@@ -20354,7 +20361,7 @@
       <c r="A378" t="s">
         <v>768</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B378" s="2" t="s">
         <v>769</v>
       </c>
       <c r="C378">
@@ -20398,7 +20405,7 @@
       <c r="A379" t="s">
         <v>770</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B379" s="2" t="s">
         <v>771</v>
       </c>
       <c r="C379">
@@ -20442,17 +20449,17 @@
       <c r="A380" t="s">
         <v>772</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B380" s="2" t="s">
         <v>773</v>
       </c>
       <c r="C380">
         <v>29700</v>
       </c>
       <c r="D380">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F380">
         <v>-1</v>
@@ -20486,17 +20493,17 @@
       <c r="A381" t="s">
         <v>774</v>
       </c>
-      <c r="B381" t="s">
+      <c r="B381" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C381">
         <v>29700</v>
       </c>
       <c r="D381">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F381">
         <v>-1</v>
@@ -20530,7 +20537,7 @@
       <c r="A382" t="s">
         <v>776</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B382" s="2" t="s">
         <v>777</v>
       </c>
       <c r="C382">
@@ -20574,17 +20581,17 @@
       <c r="A383" t="s">
         <v>778</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B383" s="2" t="s">
         <v>779</v>
       </c>
       <c r="C383">
         <v>27000</v>
       </c>
       <c r="D383">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F383">
         <v>-1</v>
@@ -20618,17 +20625,17 @@
       <c r="A384" t="s">
         <v>780</v>
       </c>
-      <c r="B384" t="s">
+      <c r="B384" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C384">
         <v>11000</v>
       </c>
       <c r="D384">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F384">
         <v>-1</v>
@@ -20662,17 +20669,17 @@
       <c r="A385" t="s">
         <v>782</v>
       </c>
-      <c r="B385" t="s">
+      <c r="B385" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C385">
         <v>3400</v>
       </c>
       <c r="D385">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F385">
         <v>-1</v>
@@ -20706,17 +20713,17 @@
       <c r="A386" t="s">
         <v>784</v>
       </c>
-      <c r="B386" t="s">
+      <c r="B386" s="2" t="s">
         <v>785</v>
       </c>
       <c r="C386">
         <v>27000</v>
       </c>
       <c r="D386">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F386">
         <v>-1</v>
@@ -20750,17 +20757,17 @@
       <c r="A387" t="s">
         <v>786</v>
       </c>
-      <c r="B387" t="s">
+      <c r="B387" s="2" t="s">
         <v>787</v>
       </c>
       <c r="C387">
         <v>11000</v>
       </c>
       <c r="D387">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F387">
         <v>-1</v>
@@ -20794,17 +20801,17 @@
       <c r="A388" t="s">
         <v>788</v>
       </c>
-      <c r="B388" t="s">
+      <c r="B388" s="2" t="s">
         <v>789</v>
       </c>
       <c r="C388">
         <v>3400</v>
       </c>
       <c r="D388">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F388">
         <v>-1</v>
@@ -20838,7 +20845,7 @@
       <c r="A389" t="s">
         <v>790</v>
       </c>
-      <c r="B389" t="s">
+      <c r="B389" s="2" t="s">
         <v>791</v>
       </c>
       <c r="C389">
@@ -20882,7 +20889,7 @@
       <c r="A390" t="s">
         <v>792</v>
       </c>
-      <c r="B390" t="s">
+      <c r="B390" s="2" t="s">
         <v>793</v>
       </c>
       <c r="C390">
@@ -20926,7 +20933,7 @@
       <c r="A391" t="s">
         <v>794</v>
       </c>
-      <c r="B391" t="s">
+      <c r="B391" s="2" t="s">
         <v>795</v>
       </c>
       <c r="C391">
@@ -20970,7 +20977,7 @@
       <c r="A392" t="s">
         <v>796</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B392" s="2" t="s">
         <v>797</v>
       </c>
       <c r="C392">
@@ -21014,7 +21021,7 @@
       <c r="A393" t="s">
         <v>798</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B393" s="2" t="s">
         <v>799</v>
       </c>
       <c r="C393">
@@ -21058,7 +21065,7 @@
       <c r="A394" t="s">
         <v>800</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B394" s="2" t="s">
         <v>801</v>
       </c>
       <c r="C394">
@@ -21102,17 +21109,17 @@
       <c r="A395" t="s">
         <v>802</v>
       </c>
-      <c r="B395" t="s">
+      <c r="B395" s="2" t="s">
         <v>803</v>
       </c>
       <c r="C395">
         <v>29500</v>
       </c>
       <c r="D395">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F395">
         <v>-1</v>
@@ -21146,17 +21153,17 @@
       <c r="A396" t="s">
         <v>804</v>
       </c>
-      <c r="B396" t="s">
+      <c r="B396" s="2" t="s">
         <v>805</v>
       </c>
       <c r="C396">
         <v>14900</v>
       </c>
       <c r="D396">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F396">
         <v>-1</v>
@@ -21190,17 +21197,17 @@
       <c r="A397" t="s">
         <v>806</v>
       </c>
-      <c r="B397" t="s">
+      <c r="B397" s="2" t="s">
         <v>807</v>
       </c>
       <c r="C397">
         <v>4900</v>
       </c>
       <c r="D397">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F397">
         <v>-1</v>
@@ -21234,17 +21241,17 @@
       <c r="A398" t="s">
         <v>808</v>
       </c>
-      <c r="B398" t="s">
+      <c r="B398" s="2" t="s">
         <v>809</v>
       </c>
       <c r="C398">
         <v>29500</v>
       </c>
       <c r="D398">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F398">
         <v>-1</v>
@@ -21278,17 +21285,17 @@
       <c r="A399" t="s">
         <v>810</v>
       </c>
-      <c r="B399" t="s">
+      <c r="B399" s="2" t="s">
         <v>811</v>
       </c>
       <c r="C399">
         <v>14900</v>
       </c>
       <c r="D399">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F399">
         <v>-1</v>
@@ -21322,17 +21329,17 @@
       <c r="A400" t="s">
         <v>812</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B400" s="2" t="s">
         <v>813</v>
       </c>
       <c r="C400">
         <v>4900</v>
       </c>
       <c r="D400">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F400">
         <v>-1</v>
@@ -21366,17 +21373,17 @@
       <c r="A401" t="s">
         <v>814</v>
       </c>
-      <c r="B401" t="s">
+      <c r="B401" s="2" t="s">
         <v>815</v>
       </c>
       <c r="C401">
         <v>8800</v>
       </c>
       <c r="D401">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>476</v>
+        <v>210</v>
       </c>
       <c r="F401">
         <v>-1</v>
@@ -21410,17 +21417,17 @@
       <c r="A402" t="s">
         <v>816</v>
       </c>
-      <c r="B402" t="s">
+      <c r="B402" s="2" t="s">
         <v>817</v>
       </c>
       <c r="C402">
         <v>8800</v>
       </c>
       <c r="D402">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>476</v>
+        <v>210</v>
       </c>
       <c r="F402">
         <v>-1</v>
@@ -21454,7 +21461,7 @@
       <c r="A403" t="s">
         <v>818</v>
       </c>
-      <c r="B403" t="s">
+      <c r="B403" s="2" t="s">
         <v>819</v>
       </c>
       <c r="C403">
@@ -21498,7 +21505,7 @@
       <c r="A404" t="s">
         <v>820</v>
       </c>
-      <c r="B404" t="s">
+      <c r="B404" s="2" t="s">
         <v>821</v>
       </c>
       <c r="C404">
@@ -21542,7 +21549,7 @@
       <c r="A405" t="s">
         <v>822</v>
       </c>
-      <c r="B405" t="s">
+      <c r="B405" s="2" t="s">
         <v>823</v>
       </c>
       <c r="C405">
@@ -21586,7 +21593,7 @@
       <c r="A406" t="s">
         <v>824</v>
       </c>
-      <c r="B406" t="s">
+      <c r="B406" s="2" t="s">
         <v>825</v>
       </c>
       <c r="C406">
@@ -21630,7 +21637,7 @@
       <c r="A407" t="s">
         <v>826</v>
       </c>
-      <c r="B407" t="s">
+      <c r="B407" s="2" t="s">
         <v>827</v>
       </c>
       <c r="C407">
@@ -21674,7 +21681,7 @@
       <c r="A408" t="s">
         <v>828</v>
       </c>
-      <c r="B408" t="s">
+      <c r="B408" s="2" t="s">
         <v>829</v>
       </c>
       <c r="C408">
@@ -21718,7 +21725,7 @@
       <c r="A409" t="s">
         <v>830</v>
       </c>
-      <c r="B409" t="s">
+      <c r="B409" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C409">
@@ -21762,17 +21769,17 @@
       <c r="A410" t="s">
         <v>832</v>
       </c>
-      <c r="B410" t="s">
+      <c r="B410" s="2" t="s">
         <v>833</v>
       </c>
       <c r="C410">
         <v>27000</v>
       </c>
       <c r="D410">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F410">
         <v>-1</v>
@@ -21806,17 +21813,17 @@
       <c r="A411" t="s">
         <v>834</v>
       </c>
-      <c r="B411" t="s">
+      <c r="B411" s="2" t="s">
         <v>835</v>
       </c>
       <c r="C411">
         <v>11000</v>
       </c>
       <c r="D411">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F411">
         <v>-1</v>
@@ -21850,17 +21857,17 @@
       <c r="A412" t="s">
         <v>836</v>
       </c>
-      <c r="B412" t="s">
+      <c r="B412" s="2" t="s">
         <v>837</v>
       </c>
       <c r="C412">
         <v>3400</v>
       </c>
       <c r="D412">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F412">
         <v>-1</v>
@@ -21894,17 +21901,17 @@
       <c r="A413" t="s">
         <v>838</v>
       </c>
-      <c r="B413" t="s">
+      <c r="B413" s="2" t="s">
         <v>839</v>
       </c>
       <c r="C413">
         <v>27000</v>
       </c>
       <c r="D413">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F413">
         <v>-1</v>
@@ -21938,17 +21945,17 @@
       <c r="A414" t="s">
         <v>840</v>
       </c>
-      <c r="B414" t="s">
+      <c r="B414" s="2" t="s">
         <v>841</v>
       </c>
       <c r="C414">
         <v>11000</v>
       </c>
       <c r="D414">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F414">
         <v>-1</v>
@@ -21982,17 +21989,17 @@
       <c r="A415" t="s">
         <v>842</v>
       </c>
-      <c r="B415" t="s">
+      <c r="B415" s="2" t="s">
         <v>843</v>
       </c>
       <c r="C415">
         <v>3400</v>
       </c>
       <c r="D415">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F415">
         <v>-1</v>
@@ -22026,7 +22033,7 @@
       <c r="A416" t="s">
         <v>844</v>
       </c>
-      <c r="B416" t="s">
+      <c r="B416" s="2" t="s">
         <v>845</v>
       </c>
       <c r="C416">
@@ -22070,7 +22077,7 @@
       <c r="A417" t="s">
         <v>846</v>
       </c>
-      <c r="B417" t="s">
+      <c r="B417" s="2" t="s">
         <v>847</v>
       </c>
       <c r="C417">
@@ -22114,7 +22121,7 @@
       <c r="A418" t="s">
         <v>848</v>
       </c>
-      <c r="B418" t="s">
+      <c r="B418" s="2" t="s">
         <v>849</v>
       </c>
       <c r="C418">
@@ -22158,17 +22165,17 @@
       <c r="A419" t="s">
         <v>850</v>
       </c>
-      <c r="B419" t="s">
+      <c r="B419" s="2" t="s">
         <v>851</v>
       </c>
       <c r="C419">
         <v>27000</v>
       </c>
       <c r="D419">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F419">
         <v>-1</v>
@@ -22202,17 +22209,17 @@
       <c r="A420" t="s">
         <v>852</v>
       </c>
-      <c r="B420" t="s">
+      <c r="B420" s="2" t="s">
         <v>853</v>
       </c>
       <c r="C420">
         <v>11000</v>
       </c>
       <c r="D420">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F420">
         <v>-1</v>
@@ -22246,17 +22253,17 @@
       <c r="A421" t="s">
         <v>854</v>
       </c>
-      <c r="B421" t="s">
+      <c r="B421" s="2" t="s">
         <v>855</v>
       </c>
       <c r="C421">
         <v>3400</v>
       </c>
       <c r="D421">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F421">
         <v>-1</v>
@@ -22290,17 +22297,17 @@
       <c r="A422" t="s">
         <v>856</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B422" s="2" t="s">
         <v>857</v>
       </c>
       <c r="C422">
         <v>27000</v>
       </c>
       <c r="D422">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F422">
         <v>-1</v>
@@ -22334,17 +22341,17 @@
       <c r="A423" t="s">
         <v>858</v>
       </c>
-      <c r="B423" t="s">
+      <c r="B423" s="2" t="s">
         <v>859</v>
       </c>
       <c r="C423">
         <v>11000</v>
       </c>
       <c r="D423">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F423">
         <v>-1</v>
@@ -22378,17 +22385,17 @@
       <c r="A424" t="s">
         <v>860</v>
       </c>
-      <c r="B424" t="s">
+      <c r="B424" s="2" t="s">
         <v>861</v>
       </c>
       <c r="C424">
         <v>3400</v>
       </c>
       <c r="D424">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F424">
         <v>-1</v>
@@ -22422,7 +22429,7 @@
       <c r="A425" t="s">
         <v>862</v>
       </c>
-      <c r="B425" t="s">
+      <c r="B425" s="2" t="s">
         <v>863</v>
       </c>
       <c r="C425">
@@ -22466,7 +22473,7 @@
       <c r="A426" t="s">
         <v>864</v>
       </c>
-      <c r="B426" t="s">
+      <c r="B426" s="2" t="s">
         <v>865</v>
       </c>
       <c r="C426">
@@ -22510,7 +22517,7 @@
       <c r="A427" t="s">
         <v>866</v>
       </c>
-      <c r="B427" t="s">
+      <c r="B427" s="2" t="s">
         <v>867</v>
       </c>
       <c r="C427">
@@ -22554,17 +22561,17 @@
       <c r="A428" t="s">
         <v>868</v>
       </c>
-      <c r="B428" t="s">
+      <c r="B428" s="2" t="s">
         <v>869</v>
       </c>
       <c r="C428">
         <v>27000</v>
       </c>
       <c r="D428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F428">
         <v>-1</v>
@@ -22598,17 +22605,17 @@
       <c r="A429" t="s">
         <v>870</v>
       </c>
-      <c r="B429" t="s">
+      <c r="B429" s="2" t="s">
         <v>871</v>
       </c>
       <c r="C429">
         <v>11000</v>
       </c>
       <c r="D429">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F429">
         <v>-1</v>
@@ -22642,17 +22649,17 @@
       <c r="A430" t="s">
         <v>872</v>
       </c>
-      <c r="B430" t="s">
+      <c r="B430" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C430">
         <v>3400</v>
       </c>
       <c r="D430">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F430">
         <v>-1</v>
@@ -22686,17 +22693,17 @@
       <c r="A431" t="s">
         <v>874</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B431" s="2" t="s">
         <v>875</v>
       </c>
       <c r="C431">
         <v>27000</v>
       </c>
       <c r="D431">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F431">
         <v>-1</v>
@@ -22730,17 +22737,17 @@
       <c r="A432" t="s">
         <v>876</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B432" s="2" t="s">
         <v>877</v>
       </c>
       <c r="C432">
         <v>11000</v>
       </c>
       <c r="D432">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F432">
         <v>-1</v>
@@ -22774,17 +22781,17 @@
       <c r="A433" t="s">
         <v>878</v>
       </c>
-      <c r="B433" t="s">
+      <c r="B433" s="2" t="s">
         <v>879</v>
       </c>
       <c r="C433">
         <v>3400</v>
       </c>
       <c r="D433">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F433">
         <v>-1</v>
@@ -22818,7 +22825,7 @@
       <c r="A434" t="s">
         <v>880</v>
       </c>
-      <c r="B434" t="s">
+      <c r="B434" s="2" t="s">
         <v>881</v>
       </c>
       <c r="C434">
@@ -22862,7 +22869,7 @@
       <c r="A435" t="s">
         <v>882</v>
       </c>
-      <c r="B435" t="s">
+      <c r="B435" s="2" t="s">
         <v>883</v>
       </c>
       <c r="C435">
@@ -22906,7 +22913,7 @@
       <c r="A436" t="s">
         <v>884</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B436" s="2" t="s">
         <v>885</v>
       </c>
       <c r="C436">
@@ -22950,17 +22957,17 @@
       <c r="A437" t="s">
         <v>886</v>
       </c>
-      <c r="B437" t="s">
+      <c r="B437" s="2" t="s">
         <v>887</v>
       </c>
       <c r="C437">
         <v>27000</v>
       </c>
       <c r="D437">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F437">
         <v>-1</v>
@@ -22994,17 +23001,17 @@
       <c r="A438" t="s">
         <v>888</v>
       </c>
-      <c r="B438" t="s">
+      <c r="B438" s="2" t="s">
         <v>889</v>
       </c>
       <c r="C438">
         <v>11000</v>
       </c>
       <c r="D438">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F438">
         <v>-1</v>
@@ -23038,17 +23045,17 @@
       <c r="A439" t="s">
         <v>890</v>
       </c>
-      <c r="B439" t="s">
+      <c r="B439" s="2" t="s">
         <v>891</v>
       </c>
       <c r="C439">
         <v>3400</v>
       </c>
       <c r="D439">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F439">
         <v>-1</v>
@@ -23082,17 +23089,17 @@
       <c r="A440" t="s">
         <v>892</v>
       </c>
-      <c r="B440" t="s">
+      <c r="B440" s="2" t="s">
         <v>893</v>
       </c>
       <c r="C440">
         <v>27000</v>
       </c>
       <c r="D440">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F440">
         <v>-1</v>
@@ -23126,17 +23133,17 @@
       <c r="A441" t="s">
         <v>894</v>
       </c>
-      <c r="B441" t="s">
+      <c r="B441" s="2" t="s">
         <v>895</v>
       </c>
       <c r="C441">
         <v>11000</v>
       </c>
       <c r="D441">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F441">
         <v>-1</v>
@@ -23170,17 +23177,17 @@
       <c r="A442" t="s">
         <v>896</v>
       </c>
-      <c r="B442" t="s">
+      <c r="B442" s="2" t="s">
         <v>897</v>
       </c>
       <c r="C442">
         <v>3400</v>
       </c>
       <c r="D442">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F442">
         <v>-1</v>
@@ -23214,7 +23221,7 @@
       <c r="A443" t="s">
         <v>898</v>
       </c>
-      <c r="B443" t="s">
+      <c r="B443" s="2" t="s">
         <v>899</v>
       </c>
       <c r="C443">
@@ -23258,7 +23265,7 @@
       <c r="A444" t="s">
         <v>900</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B444" s="2" t="s">
         <v>901</v>
       </c>
       <c r="C444">
@@ -23302,7 +23309,7 @@
       <c r="A445" t="s">
         <v>902</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B445" s="2" t="s">
         <v>903</v>
       </c>
       <c r="C445">
@@ -23346,17 +23353,17 @@
       <c r="A446" t="s">
         <v>904</v>
       </c>
-      <c r="B446" t="s">
+      <c r="B446" s="2" t="s">
         <v>905</v>
       </c>
       <c r="C446">
         <v>29500</v>
       </c>
       <c r="D446">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F446">
         <v>-1</v>
@@ -23390,17 +23397,17 @@
       <c r="A447" t="s">
         <v>906</v>
       </c>
-      <c r="B447" t="s">
+      <c r="B447" s="2" t="s">
         <v>907</v>
       </c>
       <c r="C447">
         <v>14900</v>
       </c>
       <c r="D447">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F447">
         <v>-1</v>
@@ -23434,17 +23441,17 @@
       <c r="A448" t="s">
         <v>908</v>
       </c>
-      <c r="B448" t="s">
+      <c r="B448" s="2" t="s">
         <v>909</v>
       </c>
       <c r="C448">
         <v>4900</v>
       </c>
       <c r="D448">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F448">
         <v>-1</v>
@@ -23478,17 +23485,17 @@
       <c r="A449" t="s">
         <v>910</v>
       </c>
-      <c r="B449" t="s">
+      <c r="B449" s="2" t="s">
         <v>911</v>
       </c>
       <c r="C449">
         <v>29500</v>
       </c>
       <c r="D449">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F449">
         <v>-1</v>
@@ -23522,17 +23529,17 @@
       <c r="A450" t="s">
         <v>912</v>
       </c>
-      <c r="B450" t="s">
+      <c r="B450" s="2" t="s">
         <v>913</v>
       </c>
       <c r="C450">
         <v>14900</v>
       </c>
       <c r="D450">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F450">
         <v>-1</v>
@@ -23566,17 +23573,17 @@
       <c r="A451" t="s">
         <v>914</v>
       </c>
-      <c r="B451" t="s">
+      <c r="B451" s="2" t="s">
         <v>915</v>
       </c>
       <c r="C451">
         <v>4900</v>
       </c>
       <c r="D451">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F451">
         <v>-1</v>
@@ -23610,7 +23617,7 @@
       <c r="A452" t="s">
         <v>916</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B452" s="2" t="s">
         <v>917</v>
       </c>
       <c r="C452">
@@ -23654,7 +23661,7 @@
       <c r="A453" t="s">
         <v>918</v>
       </c>
-      <c r="B453" t="s">
+      <c r="B453" s="2" t="s">
         <v>919</v>
       </c>
       <c r="C453">
@@ -23698,7 +23705,7 @@
       <c r="A454" t="s">
         <v>920</v>
       </c>
-      <c r="B454" t="s">
+      <c r="B454" s="2" t="s">
         <v>921</v>
       </c>
       <c r="C454">
@@ -23742,7 +23749,7 @@
       <c r="A455" t="s">
         <v>922</v>
       </c>
-      <c r="B455" t="s">
+      <c r="B455" s="2" t="s">
         <v>923</v>
       </c>
       <c r="C455">
@@ -23786,7 +23793,7 @@
       <c r="A456" t="s">
         <v>924</v>
       </c>
-      <c r="B456" t="s">
+      <c r="B456" s="2" t="s">
         <v>925</v>
       </c>
       <c r="C456">
@@ -23830,7 +23837,7 @@
       <c r="A457" t="s">
         <v>926</v>
       </c>
-      <c r="B457" t="s">
+      <c r="B457" s="2" t="s">
         <v>927</v>
       </c>
       <c r="C457">
@@ -23874,7 +23881,7 @@
       <c r="A458" t="s">
         <v>928</v>
       </c>
-      <c r="B458" t="s">
+      <c r="B458" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C458">
@@ -23918,7 +23925,7 @@
       <c r="A459" t="s">
         <v>930</v>
       </c>
-      <c r="B459" t="s">
+      <c r="B459" s="2" t="s">
         <v>931</v>
       </c>
       <c r="C459">
@@ -23962,7 +23969,7 @@
       <c r="A460" t="s">
         <v>932</v>
       </c>
-      <c r="B460" t="s">
+      <c r="B460" s="2" t="s">
         <v>933</v>
       </c>
       <c r="C460">
@@ -24006,17 +24013,17 @@
       <c r="A461" t="s">
         <v>934</v>
       </c>
-      <c r="B461" t="s">
+      <c r="B461" s="2" t="s">
         <v>935</v>
       </c>
       <c r="C461">
         <v>5500</v>
       </c>
       <c r="D461">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F461">
         <v>-1</v>
@@ -24050,7 +24057,7 @@
       <c r="A462" t="s">
         <v>936</v>
       </c>
-      <c r="B462" t="s">
+      <c r="B462" s="2" t="s">
         <v>937</v>
       </c>
       <c r="C462">
@@ -24094,7 +24101,7 @@
       <c r="A463" t="s">
         <v>938</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="2" t="s">
         <v>939</v>
       </c>
       <c r="C463">
@@ -24138,7 +24145,7 @@
       <c r="A464" t="s">
         <v>940</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B464" s="2" t="s">
         <v>941</v>
       </c>
       <c r="C464">
@@ -24182,17 +24189,17 @@
       <c r="A465" t="s">
         <v>942</v>
       </c>
-      <c r="B465" t="s">
+      <c r="B465" s="2" t="s">
         <v>943</v>
       </c>
       <c r="C465">
         <v>27600</v>
       </c>
       <c r="D465">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F465">
         <v>-1</v>
@@ -24226,17 +24233,17 @@
       <c r="A466" t="s">
         <v>944</v>
       </c>
-      <c r="B466" t="s">
+      <c r="B466" s="2" t="s">
         <v>945</v>
       </c>
       <c r="C466">
         <v>15600</v>
       </c>
       <c r="D466">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F466">
         <v>-1</v>
@@ -24270,17 +24277,17 @@
       <c r="A467" t="s">
         <v>946</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B467" s="2" t="s">
         <v>947</v>
       </c>
       <c r="C467">
         <v>5600</v>
       </c>
       <c r="D467">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F467">
         <v>-1</v>
@@ -24314,17 +24321,17 @@
       <c r="A468" t="s">
         <v>948</v>
       </c>
-      <c r="B468" t="s">
+      <c r="B468" s="2" t="s">
         <v>949</v>
       </c>
       <c r="C468">
         <v>27600</v>
       </c>
       <c r="D468">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F468">
         <v>-1</v>
@@ -24358,17 +24365,17 @@
       <c r="A469" t="s">
         <v>950</v>
       </c>
-      <c r="B469" t="s">
+      <c r="B469" s="2" t="s">
         <v>951</v>
       </c>
       <c r="C469">
         <v>15600</v>
       </c>
       <c r="D469">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F469">
         <v>-1</v>
@@ -24402,17 +24409,17 @@
       <c r="A470" t="s">
         <v>952</v>
       </c>
-      <c r="B470" t="s">
+      <c r="B470" s="2" t="s">
         <v>953</v>
       </c>
       <c r="C470">
         <v>5600</v>
       </c>
       <c r="D470">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F470">
         <v>-1</v>
@@ -24446,7 +24453,7 @@
       <c r="A471" t="s">
         <v>954</v>
       </c>
-      <c r="B471" t="s">
+      <c r="B471" s="2" t="s">
         <v>955</v>
       </c>
       <c r="C471">
@@ -24490,7 +24497,7 @@
       <c r="A472" t="s">
         <v>956</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B472" s="2" t="s">
         <v>957</v>
       </c>
       <c r="C472">
@@ -24534,7 +24541,7 @@
       <c r="A473" t="s">
         <v>958</v>
       </c>
-      <c r="B473" t="s">
+      <c r="B473" s="2" t="s">
         <v>959</v>
       </c>
       <c r="C473">
@@ -24578,7 +24585,7 @@
       <c r="A474" t="s">
         <v>960</v>
       </c>
-      <c r="B474" t="s">
+      <c r="B474" s="2" t="s">
         <v>961</v>
       </c>
       <c r="C474">
@@ -24622,7 +24629,7 @@
       <c r="A475" t="s">
         <v>962</v>
       </c>
-      <c r="B475" t="s">
+      <c r="B475" s="2" t="s">
         <v>963</v>
       </c>
       <c r="C475">
@@ -24666,7 +24673,7 @@
       <c r="A476" t="s">
         <v>964</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B476" s="2" t="s">
         <v>965</v>
       </c>
       <c r="C476">
@@ -24710,7 +24717,7 @@
       <c r="A477" t="s">
         <v>966</v>
       </c>
-      <c r="B477" t="s">
+      <c r="B477" s="2" t="s">
         <v>967</v>
       </c>
       <c r="C477">
@@ -24754,7 +24761,7 @@
       <c r="A478" t="s">
         <v>968</v>
       </c>
-      <c r="B478" t="s">
+      <c r="B478" s="2" t="s">
         <v>969</v>
       </c>
       <c r="C478">
@@ -24798,7 +24805,7 @@
       <c r="A479" t="s">
         <v>970</v>
       </c>
-      <c r="B479" t="s">
+      <c r="B479" s="2" t="s">
         <v>971</v>
       </c>
       <c r="C479">
@@ -24842,7 +24849,7 @@
       <c r="A480" t="s">
         <v>972</v>
       </c>
-      <c r="B480" t="s">
+      <c r="B480" s="2" t="s">
         <v>973</v>
       </c>
       <c r="C480">
@@ -24886,7 +24893,7 @@
       <c r="A481" t="s">
         <v>974</v>
       </c>
-      <c r="B481" t="s">
+      <c r="B481" s="2" t="s">
         <v>975</v>
       </c>
       <c r="C481">
@@ -24930,7 +24937,7 @@
       <c r="A482" t="s">
         <v>976</v>
       </c>
-      <c r="B482" t="s">
+      <c r="B482" s="2" t="s">
         <v>977</v>
       </c>
       <c r="C482">
@@ -24974,17 +24981,17 @@
       <c r="A483" t="s">
         <v>978</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B483" s="2" t="s">
         <v>979</v>
       </c>
       <c r="C483">
         <v>27000</v>
       </c>
       <c r="D483">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F483">
         <v>-1</v>
@@ -25018,17 +25025,17 @@
       <c r="A484" t="s">
         <v>980</v>
       </c>
-      <c r="B484" t="s">
+      <c r="B484" s="2" t="s">
         <v>981</v>
       </c>
       <c r="C484">
         <v>11000</v>
       </c>
       <c r="D484">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F484">
         <v>-1</v>
@@ -25062,17 +25069,17 @@
       <c r="A485" t="s">
         <v>982</v>
       </c>
-      <c r="B485" t="s">
+      <c r="B485" s="2" t="s">
         <v>983</v>
       </c>
       <c r="C485">
         <v>3400</v>
       </c>
       <c r="D485">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F485">
         <v>-1</v>
@@ -25106,17 +25113,17 @@
       <c r="A486" t="s">
         <v>984</v>
       </c>
-      <c r="B486" t="s">
+      <c r="B486" s="2" t="s">
         <v>985</v>
       </c>
       <c r="C486">
         <v>27000</v>
       </c>
       <c r="D486">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F486">
         <v>-1</v>
@@ -25150,17 +25157,17 @@
       <c r="A487" t="s">
         <v>986</v>
       </c>
-      <c r="B487" t="s">
+      <c r="B487" s="2" t="s">
         <v>987</v>
       </c>
       <c r="C487">
         <v>11000</v>
       </c>
       <c r="D487">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F487">
         <v>-1</v>
@@ -25194,17 +25201,17 @@
       <c r="A488" t="s">
         <v>988</v>
       </c>
-      <c r="B488" t="s">
+      <c r="B488" s="2" t="s">
         <v>989</v>
       </c>
       <c r="C488">
         <v>3400</v>
       </c>
       <c r="D488">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F488">
         <v>-1</v>
@@ -25238,7 +25245,7 @@
       <c r="A489" t="s">
         <v>990</v>
       </c>
-      <c r="B489" t="s">
+      <c r="B489" s="2" t="s">
         <v>991</v>
       </c>
       <c r="C489">
@@ -25282,7 +25289,7 @@
       <c r="A490" t="s">
         <v>992</v>
       </c>
-      <c r="B490" t="s">
+      <c r="B490" s="2" t="s">
         <v>993</v>
       </c>
       <c r="C490">
@@ -25326,7 +25333,7 @@
       <c r="A491" t="s">
         <v>994</v>
       </c>
-      <c r="B491" t="s">
+      <c r="B491" s="2" t="s">
         <v>995</v>
       </c>
       <c r="C491">
@@ -25370,17 +25377,17 @@
       <c r="A492" t="s">
         <v>996</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B492" s="2" t="s">
         <v>997</v>
       </c>
       <c r="C492">
         <v>4100</v>
       </c>
       <c r="D492">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F492">
         <v>-1</v>
@@ -25414,17 +25421,17 @@
       <c r="A493" t="s">
         <v>998</v>
       </c>
-      <c r="B493" t="s">
+      <c r="B493" s="2" t="s">
         <v>999</v>
       </c>
       <c r="C493">
         <v>11100</v>
       </c>
       <c r="D493">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F493">
         <v>-1</v>
@@ -25458,17 +25465,17 @@
       <c r="A494" t="s">
         <v>1000</v>
       </c>
-      <c r="B494" t="s">
+      <c r="B494" s="2" t="s">
         <v>1001</v>
       </c>
       <c r="C494">
         <v>20100</v>
       </c>
       <c r="D494">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F494">
         <v>-1</v>
@@ -25502,17 +25509,17 @@
       <c r="A495" t="s">
         <v>1002</v>
       </c>
-      <c r="B495" t="s">
+      <c r="B495" s="2" t="s">
         <v>1003</v>
       </c>
       <c r="C495">
         <v>30800</v>
       </c>
       <c r="D495">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F495">
         <v>-1</v>
@@ -25546,17 +25553,17 @@
       <c r="A496" t="s">
         <v>1004</v>
       </c>
-      <c r="B496" t="s">
+      <c r="B496" s="2" t="s">
         <v>1005</v>
       </c>
       <c r="C496">
         <v>8200</v>
       </c>
       <c r="D496">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F496">
         <v>-1</v>
@@ -25590,17 +25597,17 @@
       <c r="A497" t="s">
         <v>1006</v>
       </c>
-      <c r="B497" t="s">
+      <c r="B497" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="C497">
         <v>22200</v>
       </c>
       <c r="D497">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F497">
         <v>-1</v>
@@ -25634,17 +25641,17 @@
       <c r="A498" t="s">
         <v>1008</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B498" s="2" t="s">
         <v>1009</v>
       </c>
       <c r="C498">
         <v>40200</v>
       </c>
       <c r="D498">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F498">
         <v>-1</v>
@@ -25678,17 +25685,17 @@
       <c r="A499" t="s">
         <v>1010</v>
       </c>
-      <c r="B499" t="s">
+      <c r="B499" s="2" t="s">
         <v>1011</v>
       </c>
       <c r="C499">
         <v>61500</v>
       </c>
       <c r="D499">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F499">
         <v>-1</v>
@@ -25722,17 +25729,17 @@
       <c r="A500" t="s">
         <v>1012</v>
       </c>
-      <c r="B500" t="s">
+      <c r="B500" s="2" t="s">
         <v>1013</v>
       </c>
       <c r="C500">
         <v>5900</v>
       </c>
       <c r="D500">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F500">
         <v>-1</v>
@@ -25766,17 +25773,17 @@
       <c r="A501" t="s">
         <v>1014</v>
       </c>
-      <c r="B501" t="s">
+      <c r="B501" s="2" t="s">
         <v>1015</v>
       </c>
       <c r="C501">
         <v>11500</v>
       </c>
       <c r="D501">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F501">
         <v>-1</v>
@@ -25810,17 +25817,17 @@
       <c r="A502" t="s">
         <v>1016</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B502" s="2" t="s">
         <v>1017</v>
       </c>
       <c r="C502">
         <v>18100</v>
       </c>
       <c r="D502">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F502">
         <v>-1</v>
@@ -25854,17 +25861,17 @@
       <c r="A503" t="s">
         <v>1018</v>
       </c>
-      <c r="B503" t="s">
+      <c r="B503" s="2" t="s">
         <v>1019</v>
       </c>
       <c r="C503">
         <v>26000</v>
       </c>
       <c r="D503">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F503">
         <v>-1</v>
@@ -25898,17 +25905,17 @@
       <c r="A504" t="s">
         <v>1020</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B504" s="2" t="s">
         <v>1021</v>
       </c>
       <c r="C504">
         <v>11800</v>
       </c>
       <c r="D504">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F504">
         <v>-1</v>
@@ -25942,17 +25949,17 @@
       <c r="A505" t="s">
         <v>1022</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B505" s="2" t="s">
         <v>1023</v>
       </c>
       <c r="C505">
         <v>23000</v>
       </c>
       <c r="D505">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F505">
         <v>-1</v>
@@ -25986,17 +25993,17 @@
       <c r="A506" t="s">
         <v>1024</v>
       </c>
-      <c r="B506" t="s">
+      <c r="B506" s="2" t="s">
         <v>1025</v>
       </c>
       <c r="C506">
         <v>36200</v>
       </c>
       <c r="D506">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F506">
         <v>-1</v>
@@ -26030,17 +26037,17 @@
       <c r="A507" t="s">
         <v>1026</v>
       </c>
-      <c r="B507" t="s">
+      <c r="B507" s="2" t="s">
         <v>1027</v>
       </c>
       <c r="C507">
         <v>52000</v>
       </c>
       <c r="D507">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F507">
         <v>-1</v>
@@ -26074,17 +26081,17 @@
       <c r="A508" t="s">
         <v>1028</v>
       </c>
-      <c r="B508" t="s">
+      <c r="B508" s="2" t="s">
         <v>1029</v>
       </c>
       <c r="C508">
         <v>9900</v>
       </c>
       <c r="D508">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F508">
         <v>-1</v>
@@ -26118,17 +26125,17 @@
       <c r="A509" t="s">
         <v>1030</v>
       </c>
-      <c r="B509" t="s">
+      <c r="B509" s="2" t="s">
         <v>1031</v>
       </c>
       <c r="C509">
         <v>9900</v>
       </c>
       <c r="D509">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="F509">
         <v>-1</v>
@@ -26162,7 +26169,7 @@
       <c r="A510" t="s">
         <v>1032</v>
       </c>
-      <c r="B510" t="s">
+      <c r="B510" s="2" t="s">
         <v>1033</v>
       </c>
       <c r="C510">
@@ -26206,7 +26213,7 @@
       <c r="A511" t="s">
         <v>1034</v>
       </c>
-      <c r="B511" t="s">
+      <c r="B511" s="2" t="s">
         <v>1035</v>
       </c>
       <c r="C511">
@@ -26250,7 +26257,7 @@
       <c r="A512" t="s">
         <v>1036</v>
       </c>
-      <c r="B512" t="s">
+      <c r="B512" s="2" t="s">
         <v>1037</v>
       </c>
       <c r="C512">
@@ -26294,7 +26301,7 @@
       <c r="A513" t="s">
         <v>1038</v>
       </c>
-      <c r="B513" t="s">
+      <c r="B513" s="2" t="s">
         <v>1039</v>
       </c>
       <c r="C513">
@@ -26338,7 +26345,7 @@
       <c r="A514" t="s">
         <v>1040</v>
       </c>
-      <c r="B514" t="s">
+      <c r="B514" s="2" t="s">
         <v>1041</v>
       </c>
       <c r="C514">
@@ -26382,7 +26389,7 @@
       <c r="A515" t="s">
         <v>1042</v>
       </c>
-      <c r="B515" t="s">
+      <c r="B515" s="2" t="s">
         <v>1043</v>
       </c>
       <c r="C515">
@@ -26426,7 +26433,7 @@
       <c r="A516" t="s">
         <v>1044</v>
       </c>
-      <c r="B516" t="s">
+      <c r="B516" s="2" t="s">
         <v>1045</v>
       </c>
       <c r="C516">
@@ -26470,7 +26477,7 @@
       <c r="A517" t="s">
         <v>1046</v>
       </c>
-      <c r="B517" t="s">
+      <c r="B517" s="2" t="s">
         <v>1047</v>
       </c>
       <c r="C517">
@@ -26514,7 +26521,7 @@
       <c r="A518" t="s">
         <v>1048</v>
       </c>
-      <c r="B518" t="s">
+      <c r="B518" s="2" t="s">
         <v>1049</v>
       </c>
       <c r="C518">
@@ -26558,17 +26565,17 @@
       <c r="A519" t="s">
         <v>1050</v>
       </c>
-      <c r="B519" t="s">
+      <c r="B519" s="2" t="s">
         <v>1051</v>
       </c>
       <c r="C519">
         <v>7900</v>
       </c>
       <c r="D519">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F519">
         <v>-1</v>
@@ -26602,17 +26609,17 @@
       <c r="A520" t="s">
         <v>1052</v>
       </c>
-      <c r="B520" t="s">
+      <c r="B520" s="2" t="s">
         <v>1053</v>
       </c>
       <c r="C520">
         <v>1200</v>
       </c>
       <c r="D520">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F520">
         <v>-1</v>
@@ -26646,17 +26653,17 @@
       <c r="A521" t="s">
         <v>1054</v>
       </c>
-      <c r="B521" t="s">
+      <c r="B521" s="2" t="s">
         <v>1055</v>
       </c>
       <c r="C521">
         <v>2000</v>
       </c>
       <c r="D521">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F521">
         <v>-1</v>
@@ -26690,17 +26697,17 @@
       <c r="A522" t="s">
         <v>1056</v>
       </c>
-      <c r="B522" t="s">
+      <c r="B522" s="2" t="s">
         <v>1057</v>
       </c>
       <c r="C522">
         <v>3000</v>
       </c>
       <c r="D522">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F522">
         <v>-1</v>
@@ -26734,17 +26741,17 @@
       <c r="A523" t="s">
         <v>1058</v>
       </c>
-      <c r="B523" t="s">
+      <c r="B523" s="2" t="s">
         <v>1059</v>
       </c>
       <c r="C523">
         <v>4800</v>
       </c>
       <c r="D523">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E523" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F523">
         <v>-1</v>
@@ -26778,7 +26785,7 @@
       <c r="A524" t="s">
         <v>1060</v>
       </c>
-      <c r="B524" t="s">
+      <c r="B524" s="2" t="s">
         <v>1061</v>
       </c>
       <c r="C524">
@@ -26822,7 +26829,7 @@
       <c r="A525" t="s">
         <v>1062</v>
       </c>
-      <c r="B525" t="s">
+      <c r="B525" s="2" t="s">
         <v>1063</v>
       </c>
       <c r="C525">
@@ -26866,7 +26873,7 @@
       <c r="A526" t="s">
         <v>1064</v>
       </c>
-      <c r="B526" t="s">
+      <c r="B526" s="2" t="s">
         <v>1065</v>
       </c>
       <c r="C526">
@@ -26910,7 +26917,7 @@
       <c r="A527" t="s">
         <v>1066</v>
       </c>
-      <c r="B527" t="s">
+      <c r="B527" s="2" t="s">
         <v>1067</v>
       </c>
       <c r="C527">
@@ -26954,7 +26961,7 @@
       <c r="A528" t="s">
         <v>1068</v>
       </c>
-      <c r="B528" t="s">
+      <c r="B528" s="2" t="s">
         <v>1069</v>
       </c>
       <c r="C528">
@@ -26998,7 +27005,7 @@
       <c r="A529" t="s">
         <v>1070</v>
       </c>
-      <c r="B529" t="s">
+      <c r="B529" s="2" t="s">
         <v>1071</v>
       </c>
       <c r="C529">
@@ -27042,7 +27049,7 @@
       <c r="A530" t="s">
         <v>1072</v>
       </c>
-      <c r="B530" t="s">
+      <c r="B530" s="2" t="s">
         <v>1073</v>
       </c>
       <c r="C530">
@@ -27086,7 +27093,7 @@
       <c r="A531" t="s">
         <v>1074</v>
       </c>
-      <c r="B531" t="s">
+      <c r="B531" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="C531">
@@ -27130,17 +27137,17 @@
       <c r="A532" t="s">
         <v>1076</v>
       </c>
-      <c r="B532" t="s">
+      <c r="B532" s="2" t="s">
         <v>1077</v>
       </c>
       <c r="C532">
         <v>2900</v>
       </c>
       <c r="D532">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F532">
         <v>-1</v>
@@ -27174,7 +27181,7 @@
       <c r="A533" t="s">
         <v>1078</v>
       </c>
-      <c r="B533" t="s">
+      <c r="B533" s="2" t="s">
         <v>1079</v>
       </c>
       <c r="C533">
@@ -27218,7 +27225,7 @@
       <c r="A534" t="s">
         <v>1080</v>
       </c>
-      <c r="B534" t="s">
+      <c r="B534" s="2" t="s">
         <v>1081</v>
       </c>
       <c r="C534">
@@ -27262,17 +27269,17 @@
       <c r="A535" t="s">
         <v>1082</v>
       </c>
-      <c r="B535" t="s">
+      <c r="B535" s="2" t="s">
         <v>1083</v>
       </c>
       <c r="C535">
         <v>2900</v>
       </c>
       <c r="D535">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F535">
         <v>-1</v>
@@ -27306,17 +27313,17 @@
       <c r="A536" t="s">
         <v>1084</v>
       </c>
-      <c r="B536" t="s">
+      <c r="B536" s="2" t="s">
         <v>1085</v>
       </c>
       <c r="C536">
         <v>14900</v>
       </c>
       <c r="D536">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F536">
         <v>-1</v>
@@ -27350,17 +27357,17 @@
       <c r="A537" t="s">
         <v>1086</v>
       </c>
-      <c r="B537" t="s">
+      <c r="B537" s="2" t="s">
         <v>1087</v>
       </c>
       <c r="C537">
         <v>2500</v>
       </c>
       <c r="D537">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F537">
         <v>-1</v>
@@ -27394,17 +27401,17 @@
       <c r="A538" t="s">
         <v>1088</v>
       </c>
-      <c r="B538" t="s">
+      <c r="B538" s="2" t="s">
         <v>1089</v>
       </c>
       <c r="C538">
         <v>2500</v>
       </c>
       <c r="D538">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F538">
         <v>-1</v>
@@ -27438,7 +27445,7 @@
       <c r="A539" t="s">
         <v>1090</v>
       </c>
-      <c r="B539" t="s">
+      <c r="B539" s="2" t="s">
         <v>1091</v>
       </c>
       <c r="C539">
@@ -27482,7 +27489,7 @@
       <c r="A540" t="s">
         <v>1092</v>
       </c>
-      <c r="B540" t="s">
+      <c r="B540" s="2" t="s">
         <v>1093</v>
       </c>
       <c r="C540">
@@ -27526,7 +27533,7 @@
       <c r="A541" t="s">
         <v>1094</v>
       </c>
-      <c r="B541" t="s">
+      <c r="B541" s="2" t="s">
         <v>1093</v>
       </c>
       <c r="C541">
@@ -27570,7 +27577,7 @@
       <c r="A542" t="s">
         <v>1095</v>
       </c>
-      <c r="B542" t="s">
+      <c r="B542" s="2" t="s">
         <v>1093</v>
       </c>
       <c r="C542">
@@ -27614,7 +27621,7 @@
       <c r="A543" t="s">
         <v>1096</v>
       </c>
-      <c r="B543" t="s">
+      <c r="B543" s="2" t="s">
         <v>1097</v>
       </c>
       <c r="C543">
@@ -27658,17 +27665,17 @@
       <c r="A544" t="s">
         <v>1098</v>
       </c>
-      <c r="B544" t="s">
+      <c r="B544" s="2" t="s">
         <v>1099</v>
       </c>
       <c r="C544">
         <v>31500</v>
       </c>
       <c r="D544">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F544">
         <v>-1</v>
@@ -27702,7 +27709,7 @@
       <c r="A545" t="s">
         <v>1100</v>
       </c>
-      <c r="B545" t="s">
+      <c r="B545" s="2" t="s">
         <v>1101</v>
       </c>
       <c r="C545">
@@ -27746,17 +27753,17 @@
       <c r="A546" t="s">
         <v>1102</v>
       </c>
-      <c r="B546" t="s">
+      <c r="B546" s="2" t="s">
         <v>1103</v>
       </c>
       <c r="C546">
         <v>1100</v>
       </c>
       <c r="D546">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F546">
         <v>-1</v>
@@ -27790,7 +27797,7 @@
       <c r="A547" t="s">
         <v>1104</v>
       </c>
-      <c r="B547" t="s">
+      <c r="B547" s="2" t="s">
         <v>1105</v>
       </c>
       <c r="C547">
@@ -27834,7 +27841,7 @@
       <c r="A548" t="s">
         <v>1106</v>
       </c>
-      <c r="B548" t="s">
+      <c r="B548" s="2" t="s">
         <v>1107</v>
       </c>
       <c r="C548">
@@ -27878,7 +27885,7 @@
       <c r="A549" t="s">
         <v>1108</v>
       </c>
-      <c r="B549" t="s">
+      <c r="B549" s="2" t="s">
         <v>1109</v>
       </c>
       <c r="C549">
@@ -27922,7 +27929,7 @@
       <c r="A550" t="s">
         <v>1110</v>
       </c>
-      <c r="B550" t="s">
+      <c r="B550" s="2" t="s">
         <v>1111</v>
       </c>
       <c r="C550">
@@ -27966,7 +27973,7 @@
       <c r="A551" t="s">
         <v>1112</v>
       </c>
-      <c r="B551" t="s">
+      <c r="B551" s="2" t="s">
         <v>1113</v>
       </c>
       <c r="C551">
@@ -28010,7 +28017,7 @@
       <c r="A552" t="s">
         <v>1114</v>
       </c>
-      <c r="B552" t="s">
+      <c r="B552" s="2" t="s">
         <v>1115</v>
       </c>
       <c r="C552">
@@ -28054,7 +28061,7 @@
       <c r="A553" t="s">
         <v>1116</v>
       </c>
-      <c r="B553" t="s">
+      <c r="B553" s="2" t="s">
         <v>1117</v>
       </c>
       <c r="C553">

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,19 +3,30 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CFA4C0-8F1E-4D72-9079-1473757098E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95469090-8A5A-4BD1-B352-0D18D29ACB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CashShop" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1116">
   <si>
     <t>string[64]</t>
   </si>
@@ -1910,15 +1921,9 @@
     <t>cash307</t>
   </si>
   <si>
-    <t>iywsu02</t>
-  </si>
-  <si>
     <t>cash308</t>
   </si>
   <si>
-    <t>iycsa56</t>
-  </si>
-  <si>
     <t>cash309</t>
   </si>
   <si>
@@ -3305,70 +3310,70 @@
     <t>cash540</t>
   </si>
   <si>
+    <t>cash545</t>
+  </si>
+  <si>
+    <t>cash546</t>
+  </si>
+  <si>
+    <t>cash547</t>
+  </si>
+  <si>
+    <t>cash548</t>
+  </si>
+  <si>
+    <t>cash549</t>
+  </si>
+  <si>
+    <t>ircja09</t>
+  </si>
+  <si>
+    <t>cash550</t>
+  </si>
+  <si>
+    <t>ircja10</t>
+  </si>
+  <si>
+    <t>cash551</t>
+  </si>
+  <si>
+    <t>ircja11</t>
+  </si>
+  <si>
+    <t>ipcsh07</t>
+  </si>
+  <si>
+    <t>ipcsh04</t>
+  </si>
+  <si>
+    <t>ipcsh05</t>
+  </si>
+  <si>
+    <t>ipcsh06</t>
+  </si>
+  <si>
+    <t>ippms02</t>
+  </si>
+  <si>
+    <t>ippms03</t>
+  </si>
+  <si>
+    <t>ippms04</t>
+  </si>
+  <si>
+    <t>ippms05</t>
+  </si>
+  <si>
     <t>cash541</t>
   </si>
   <si>
-    <t>bxeup04</t>
-  </si>
-  <si>
     <t>cash542</t>
   </si>
   <si>
-    <t>bxeup05</t>
-  </si>
-  <si>
     <t>cash543</t>
   </si>
   <si>
-    <t>bxeup06</t>
-  </si>
-  <si>
     <t>cash544</t>
-  </si>
-  <si>
-    <t>ipcal03</t>
-  </si>
-  <si>
-    <t>cash545</t>
-  </si>
-  <si>
-    <t>ipwhp03</t>
-  </si>
-  <si>
-    <t>cash546</t>
-  </si>
-  <si>
-    <t>ipwed01</t>
-  </si>
-  <si>
-    <t>cash547</t>
-  </si>
-  <si>
-    <t>ipfhp01</t>
-  </si>
-  <si>
-    <t>cash548</t>
-  </si>
-  <si>
-    <t>ipcur01</t>
-  </si>
-  <si>
-    <t>cash549</t>
-  </si>
-  <si>
-    <t>ircja09</t>
-  </si>
-  <si>
-    <t>cash550</t>
-  </si>
-  <si>
-    <t>ircja10</t>
-  </si>
-  <si>
-    <t>cash551</t>
-  </si>
-  <si>
-    <t>ircja11</t>
   </si>
 </sst>
 </file>
@@ -3385,7 +3390,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3395,6 +3400,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3411,10 +3428,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3862,7 +3881,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>1109</v>
       </c>
       <c r="C3">
         <v>1100</v>
@@ -3906,7 +3925,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>1110</v>
       </c>
       <c r="C4">
         <v>1100</v>
@@ -3950,7 +3969,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>1107</v>
       </c>
       <c r="C5">
         <v>2200</v>
@@ -3994,7 +4013,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>1109</v>
       </c>
       <c r="C6">
         <v>1100</v>
@@ -4038,7 +4057,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>1110</v>
       </c>
       <c r="C7">
         <v>1100</v>
@@ -4082,7 +4101,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>1107</v>
       </c>
       <c r="C8">
         <v>2200</v>
@@ -4126,7 +4145,7 @@
         <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>1109</v>
       </c>
       <c r="C9">
         <v>1100</v>
@@ -4170,7 +4189,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>1110</v>
       </c>
       <c r="C10">
         <v>1100</v>
@@ -4214,7 +4233,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>1107</v>
       </c>
       <c r="C11">
         <v>2200</v>
@@ -4264,10 +4283,10 @@
         <v>200</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -4396,10 +4415,10 @@
         <v>200</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -4528,10 +4547,10 @@
         <v>200</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -4704,10 +4723,10 @@
         <v>300</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -4748,10 +4767,10 @@
         <v>300</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -5012,10 +5031,10 @@
         <v>300</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F29">
         <v>-1</v>
@@ -5100,10 +5119,10 @@
         <v>300</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F31">
         <v>-1</v>
@@ -5276,10 +5295,10 @@
         <v>300</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F35">
         <v>-1</v>
@@ -5496,10 +5515,10 @@
         <v>300</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F40">
         <v>-1</v>
@@ -5540,10 +5559,10 @@
         <v>400</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F41">
         <v>-1</v>
@@ -7696,10 +7715,10 @@
         <v>200</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F90">
         <v>-1</v>
@@ -7828,10 +7847,10 @@
         <v>500</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F93">
         <v>-1</v>
@@ -7960,10 +7979,10 @@
         <v>900</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F96">
         <v>-1</v>
@@ -9632,10 +9651,10 @@
         <v>150</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F134">
         <v>-1</v>
@@ -9764,10 +9783,10 @@
         <v>150</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F137">
         <v>-1</v>
@@ -11700,10 +11719,10 @@
         <v>750</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F181">
         <v>-1</v>
@@ -11744,10 +11763,10 @@
         <v>750</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F182">
         <v>-1</v>
@@ -11788,10 +11807,10 @@
         <v>2800</v>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F183">
         <v>-1</v>
@@ -11832,10 +11851,10 @@
         <v>2800</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F184">
         <v>-1</v>
@@ -11876,10 +11895,10 @@
         <v>2800</v>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F185">
         <v>-1</v>
@@ -11920,10 +11939,10 @@
         <v>2800</v>
       </c>
       <c r="D186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F186">
         <v>-1</v>
@@ -12756,10 +12775,10 @@
         <v>1100</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F205">
         <v>-1</v>
@@ -12800,10 +12819,10 @@
         <v>1100</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F206">
         <v>-1</v>
@@ -12888,10 +12907,10 @@
         <v>1100</v>
       </c>
       <c r="D208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F208">
         <v>-1</v>
@@ -12932,10 +12951,10 @@
         <v>1100</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F209">
         <v>-1</v>
@@ -15088,10 +15107,10 @@
         <v>150</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>528</v>
+        <v>210</v>
       </c>
       <c r="F258">
         <v>-1</v>
@@ -15132,10 +15151,10 @@
         <v>150</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>528</v>
+        <v>210</v>
       </c>
       <c r="F259">
         <v>-1</v>
@@ -15176,10 +15195,10 @@
         <v>150</v>
       </c>
       <c r="D260">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>528</v>
+        <v>210</v>
       </c>
       <c r="F260">
         <v>-1</v>
@@ -15220,10 +15239,10 @@
         <v>50</v>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>528</v>
+        <v>210</v>
       </c>
       <c r="F261">
         <v>-1</v>
@@ -15264,10 +15283,10 @@
         <v>50</v>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>528</v>
+        <v>210</v>
       </c>
       <c r="F262">
         <v>-1</v>
@@ -15308,10 +15327,10 @@
         <v>50</v>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>528</v>
+        <v>210</v>
       </c>
       <c r="F263">
         <v>-1</v>
@@ -15352,10 +15371,10 @@
         <v>500</v>
       </c>
       <c r="D264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F264">
         <v>-1</v>
@@ -15396,10 +15415,10 @@
         <v>500</v>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F265">
         <v>-1</v>
@@ -15440,10 +15459,10 @@
         <v>500</v>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F266">
         <v>-1</v>
@@ -17326,16 +17345,16 @@
         <v>630</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="C309">
         <v>6800</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="F309">
         <v>-1</v>
@@ -17367,19 +17386,19 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C310">
         <v>7500</v>
       </c>
       <c r="D310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="F310">
         <v>-1</v>
@@ -17411,10 +17430,10 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C311">
         <v>5300</v>
@@ -17455,10 +17474,10 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C312">
         <v>2600</v>
@@ -17499,10 +17518,10 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C313">
         <v>1300</v>
@@ -17543,10 +17562,10 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C314">
         <v>4300</v>
@@ -17587,10 +17606,10 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C315">
         <v>6500</v>
@@ -17631,10 +17650,10 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C316">
         <v>9900</v>
@@ -17675,10 +17694,10 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C317">
         <v>5300</v>
@@ -17719,10 +17738,10 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C318">
         <v>7500</v>
@@ -17763,10 +17782,10 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C319">
         <v>10900</v>
@@ -17807,10 +17826,10 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C320">
         <v>6300</v>
@@ -17851,10 +17870,10 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C321">
         <v>8500</v>
@@ -17895,10 +17914,10 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C322">
         <v>11900</v>
@@ -17939,10 +17958,10 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C323">
         <v>5800</v>
@@ -17983,10 +18002,10 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C324">
         <v>10500</v>
@@ -18027,10 +18046,10 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C325">
         <v>19600</v>
@@ -18071,10 +18090,10 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C326">
         <v>6800</v>
@@ -18115,10 +18134,10 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C327">
         <v>11500</v>
@@ -18159,10 +18178,10 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C328">
         <v>20600</v>
@@ -18203,10 +18222,10 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C329">
         <v>7800</v>
@@ -18247,10 +18266,10 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C330">
         <v>12500</v>
@@ -18291,10 +18310,10 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C331">
         <v>21600</v>
@@ -18335,10 +18354,10 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C332">
         <v>37500</v>
@@ -18379,10 +18398,10 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C333">
         <v>37500</v>
@@ -18423,10 +18442,10 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C334">
         <v>37500</v>
@@ -18467,19 +18486,19 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C335">
         <v>65500</v>
       </c>
       <c r="D335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F335">
         <v>-1</v>
@@ -18511,10 +18530,10 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C336">
         <v>65500</v>
@@ -18555,19 +18574,19 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C337">
         <v>65500</v>
       </c>
       <c r="D337">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F337">
         <v>-1</v>
@@ -18599,19 +18618,19 @@
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C338">
         <v>63000</v>
       </c>
       <c r="D338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F338">
         <v>-1</v>
@@ -18643,10 +18662,10 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C339">
         <v>63000</v>
@@ -18687,19 +18706,19 @@
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C340">
         <v>63000</v>
       </c>
       <c r="D340">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F340">
         <v>-1</v>
@@ -18731,19 +18750,19 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C341">
         <v>63000</v>
       </c>
       <c r="D341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F341">
         <v>-1</v>
@@ -18775,10 +18794,10 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C342">
         <v>63000</v>
@@ -18819,19 +18838,19 @@
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C343">
         <v>63000</v>
       </c>
       <c r="D343">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F343">
         <v>-1</v>
@@ -18863,19 +18882,19 @@
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C344">
         <v>57000</v>
       </c>
       <c r="D344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F344">
         <v>-1</v>
@@ -18907,10 +18926,10 @@
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C345">
         <v>57000</v>
@@ -18951,19 +18970,19 @@
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C346">
         <v>57000</v>
       </c>
       <c r="D346">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F346">
         <v>-1</v>
@@ -18995,19 +19014,19 @@
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C347">
         <v>60000</v>
       </c>
       <c r="D347">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F347">
         <v>-1</v>
@@ -19039,10 +19058,10 @@
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C348">
         <v>60000</v>
@@ -19083,19 +19102,19 @@
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C349">
         <v>60000</v>
       </c>
       <c r="D349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F349">
         <v>-1</v>
@@ -19127,19 +19146,19 @@
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C350">
         <v>48000</v>
       </c>
       <c r="D350">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F350">
         <v>-1</v>
@@ -19171,10 +19190,10 @@
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C351">
         <v>48000</v>
@@ -19215,19 +19234,19 @@
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C352">
         <v>48000</v>
       </c>
       <c r="D352">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F352">
         <v>-1</v>
@@ -19259,19 +19278,19 @@
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C353">
         <v>41000</v>
       </c>
       <c r="D353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F353">
         <v>-1</v>
@@ -19303,10 +19322,10 @@
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C354">
         <v>41000</v>
@@ -19347,19 +19366,19 @@
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C355">
         <v>41000</v>
       </c>
       <c r="D355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F355">
         <v>-1</v>
@@ -19391,19 +19410,19 @@
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C356">
         <v>41000</v>
       </c>
       <c r="D356">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F356">
         <v>-1</v>
@@ -19435,10 +19454,10 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C357">
         <v>41000</v>
@@ -19479,19 +19498,19 @@
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C358">
         <v>41000</v>
       </c>
       <c r="D358">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F358">
         <v>-1</v>
@@ -19523,19 +19542,19 @@
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C359">
         <v>41000</v>
       </c>
       <c r="D359">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F359">
         <v>-1</v>
@@ -19567,10 +19586,10 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C360">
         <v>41000</v>
@@ -19611,19 +19630,19 @@
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C361">
         <v>41000</v>
       </c>
       <c r="D361">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F361">
         <v>-1</v>
@@ -19655,19 +19674,19 @@
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C362">
         <v>38000</v>
       </c>
       <c r="D362">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F362">
         <v>-1</v>
@@ -19699,10 +19718,10 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C363">
         <v>38000</v>
@@ -19743,19 +19762,19 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C364">
         <v>38000</v>
       </c>
       <c r="D364">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F364">
         <v>-1</v>
@@ -19787,19 +19806,19 @@
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C365">
         <v>38000</v>
       </c>
       <c r="D365">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F365">
         <v>-1</v>
@@ -19831,10 +19850,10 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C366">
         <v>38000</v>
@@ -19875,19 +19894,19 @@
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C367">
         <v>38000</v>
       </c>
       <c r="D367">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F367">
         <v>-1</v>
@@ -19919,10 +19938,10 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C368">
         <v>41000</v>
@@ -19963,10 +19982,10 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C369">
         <v>41000</v>
@@ -20007,19 +20026,19 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C370">
         <v>41000</v>
       </c>
       <c r="D370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F370">
         <v>-1</v>
@@ -20051,10 +20070,10 @@
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C371">
         <v>32500</v>
@@ -20095,10 +20114,10 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C372">
         <v>19500</v>
@@ -20139,10 +20158,10 @@
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C373">
         <v>9750</v>
@@ -20183,10 +20202,10 @@
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C374">
         <v>32500</v>
@@ -20227,10 +20246,10 @@
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C375">
         <v>19500</v>
@@ -20271,10 +20290,10 @@
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C376">
         <v>9750</v>
@@ -20315,19 +20334,19 @@
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C377">
         <v>32500</v>
       </c>
       <c r="D377">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F377">
         <v>-1</v>
@@ -20359,19 +20378,19 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C378">
         <v>19500</v>
       </c>
       <c r="D378">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F378">
         <v>-1</v>
@@ -20403,19 +20422,19 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C379">
         <v>9750</v>
       </c>
       <c r="D379">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F379">
         <v>-1</v>
@@ -20447,10 +20466,10 @@
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C380">
         <v>29700</v>
@@ -20491,10 +20510,10 @@
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C381">
         <v>29700</v>
@@ -20535,19 +20554,19 @@
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C382">
         <v>29700</v>
       </c>
       <c r="D382">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F382">
         <v>-1</v>
@@ -20579,10 +20598,10 @@
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C383">
         <v>27000</v>
@@ -20623,10 +20642,10 @@
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C384">
         <v>11000</v>
@@ -20667,10 +20686,10 @@
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C385">
         <v>3400</v>
@@ -20711,10 +20730,10 @@
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C386">
         <v>27000</v>
@@ -20755,10 +20774,10 @@
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C387">
         <v>11000</v>
@@ -20799,10 +20818,10 @@
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C388">
         <v>3400</v>
@@ -20843,19 +20862,19 @@
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C389">
         <v>27000</v>
       </c>
       <c r="D389">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F389">
         <v>-1</v>
@@ -20887,19 +20906,19 @@
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C390">
         <v>11000</v>
       </c>
       <c r="D390">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F390">
         <v>-1</v>
@@ -20931,19 +20950,19 @@
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C391">
         <v>3400</v>
       </c>
       <c r="D391">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F391">
         <v>-1</v>
@@ -20975,19 +20994,19 @@
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C392">
         <v>29500</v>
       </c>
       <c r="D392">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F392">
         <v>-1</v>
@@ -21019,19 +21038,19 @@
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C393">
         <v>14900</v>
       </c>
       <c r="D393">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F393">
         <v>-1</v>
@@ -21063,19 +21082,19 @@
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C394">
         <v>4900</v>
       </c>
       <c r="D394">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F394">
         <v>-1</v>
@@ -21107,10 +21126,10 @@
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C395">
         <v>29500</v>
@@ -21151,10 +21170,10 @@
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C396">
         <v>14900</v>
@@ -21195,10 +21214,10 @@
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C397">
         <v>4900</v>
@@ -21239,10 +21258,10 @@
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C398">
         <v>29500</v>
@@ -21283,10 +21302,10 @@
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C399">
         <v>14900</v>
@@ -21327,10 +21346,10 @@
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C400">
         <v>4900</v>
@@ -21371,10 +21390,10 @@
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C401">
         <v>8800</v>
@@ -21415,10 +21434,10 @@
     </row>
     <row r="402" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C402">
         <v>8800</v>
@@ -21459,19 +21478,19 @@
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C403">
         <v>8800</v>
       </c>
       <c r="D403">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>476</v>
+        <v>210</v>
       </c>
       <c r="F403">
         <v>-1</v>
@@ -21503,10 +21522,10 @@
     </row>
     <row r="404" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C404">
         <v>26500</v>
@@ -21547,10 +21566,10 @@
     </row>
     <row r="405" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C405">
         <v>29500</v>
@@ -21591,10 +21610,10 @@
     </row>
     <row r="406" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C406">
         <v>35500</v>
@@ -21635,19 +21654,19 @@
     </row>
     <row r="407" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C407">
         <v>27000</v>
       </c>
       <c r="D407">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F407">
         <v>-1</v>
@@ -21679,19 +21698,19 @@
     </row>
     <row r="408" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C408">
         <v>11000</v>
       </c>
       <c r="D408">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F408">
         <v>-1</v>
@@ -21723,19 +21742,19 @@
     </row>
     <row r="409" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C409">
         <v>3400</v>
       </c>
       <c r="D409">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F409">
         <v>-1</v>
@@ -21767,10 +21786,10 @@
     </row>
     <row r="410" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C410">
         <v>27000</v>
@@ -21811,10 +21830,10 @@
     </row>
     <row r="411" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C411">
         <v>11000</v>
@@ -21855,10 +21874,10 @@
     </row>
     <row r="412" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C412">
         <v>3400</v>
@@ -21899,10 +21918,10 @@
     </row>
     <row r="413" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C413">
         <v>27000</v>
@@ -21943,10 +21962,10 @@
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C414">
         <v>11000</v>
@@ -21987,10 +22006,10 @@
     </row>
     <row r="415" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C415">
         <v>3400</v>
@@ -22031,19 +22050,19 @@
     </row>
     <row r="416" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C416">
         <v>27000</v>
       </c>
       <c r="D416">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F416">
         <v>-1</v>
@@ -22075,19 +22094,19 @@
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C417">
         <v>11000</v>
       </c>
       <c r="D417">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F417">
         <v>-1</v>
@@ -22119,19 +22138,19 @@
     </row>
     <row r="418" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C418">
         <v>3400</v>
       </c>
       <c r="D418">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F418">
         <v>-1</v>
@@ -22163,10 +22182,10 @@
     </row>
     <row r="419" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C419">
         <v>27000</v>
@@ -22207,10 +22226,10 @@
     </row>
     <row r="420" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C420">
         <v>11000</v>
@@ -22251,10 +22270,10 @@
     </row>
     <row r="421" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C421">
         <v>3400</v>
@@ -22295,10 +22314,10 @@
     </row>
     <row r="422" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C422">
         <v>27000</v>
@@ -22339,10 +22358,10 @@
     </row>
     <row r="423" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C423">
         <v>11000</v>
@@ -22383,10 +22402,10 @@
     </row>
     <row r="424" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C424">
         <v>3400</v>
@@ -22427,19 +22446,19 @@
     </row>
     <row r="425" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C425">
         <v>27000</v>
       </c>
       <c r="D425">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F425">
         <v>-1</v>
@@ -22471,19 +22490,19 @@
     </row>
     <row r="426" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C426">
         <v>11000</v>
       </c>
       <c r="D426">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F426">
         <v>-1</v>
@@ -22515,19 +22534,19 @@
     </row>
     <row r="427" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C427">
         <v>3400</v>
       </c>
       <c r="D427">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F427">
         <v>-1</v>
@@ -22559,10 +22578,10 @@
     </row>
     <row r="428" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C428">
         <v>27000</v>
@@ -22603,10 +22622,10 @@
     </row>
     <row r="429" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C429">
         <v>11000</v>
@@ -22647,10 +22666,10 @@
     </row>
     <row r="430" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C430">
         <v>3400</v>
@@ -22691,10 +22710,10 @@
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C431">
         <v>27000</v>
@@ -22735,10 +22754,10 @@
     </row>
     <row r="432" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C432">
         <v>11000</v>
@@ -22779,10 +22798,10 @@
     </row>
     <row r="433" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C433">
         <v>3400</v>
@@ -22823,19 +22842,19 @@
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C434">
         <v>27000</v>
       </c>
       <c r="D434">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F434">
         <v>-1</v>
@@ -22867,19 +22886,19 @@
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C435">
         <v>11000</v>
       </c>
       <c r="D435">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F435">
         <v>-1</v>
@@ -22911,19 +22930,19 @@
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C436">
         <v>3400</v>
       </c>
       <c r="D436">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F436">
         <v>-1</v>
@@ -22955,10 +22974,10 @@
     </row>
     <row r="437" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C437">
         <v>27000</v>
@@ -22999,10 +23018,10 @@
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C438">
         <v>11000</v>
@@ -23043,10 +23062,10 @@
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C439">
         <v>3400</v>
@@ -23087,10 +23106,10 @@
     </row>
     <row r="440" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C440">
         <v>27000</v>
@@ -23131,10 +23150,10 @@
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C441">
         <v>11000</v>
@@ -23175,10 +23194,10 @@
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C442">
         <v>3400</v>
@@ -23219,19 +23238,19 @@
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C443">
         <v>29500</v>
       </c>
       <c r="D443">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F443">
         <v>-1</v>
@@ -23263,19 +23282,19 @@
     </row>
     <row r="444" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C444">
         <v>14900</v>
       </c>
       <c r="D444">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F444">
         <v>-1</v>
@@ -23307,19 +23326,19 @@
     </row>
     <row r="445" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C445">
         <v>4900</v>
       </c>
       <c r="D445">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F445">
         <v>-1</v>
@@ -23351,10 +23370,10 @@
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C446">
         <v>29500</v>
@@ -23395,10 +23414,10 @@
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C447">
         <v>14900</v>
@@ -23439,10 +23458,10 @@
     </row>
     <row r="448" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C448">
         <v>4900</v>
@@ -23483,10 +23502,10 @@
     </row>
     <row r="449" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C449">
         <v>29500</v>
@@ -23527,10 +23546,10 @@
     </row>
     <row r="450" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C450">
         <v>14900</v>
@@ -23571,10 +23590,10 @@
     </row>
     <row r="451" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C451">
         <v>4900</v>
@@ -23615,10 +23634,10 @@
     </row>
     <row r="452" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C452">
         <v>8800</v>
@@ -23659,10 +23678,10 @@
     </row>
     <row r="453" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C453">
         <v>8800</v>
@@ -23703,10 +23722,10 @@
     </row>
     <row r="454" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C454">
         <v>8800</v>
@@ -23747,10 +23766,10 @@
     </row>
     <row r="455" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C455">
         <v>8800</v>
@@ -23791,10 +23810,10 @@
     </row>
     <row r="456" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C456">
         <v>8800</v>
@@ -23835,10 +23854,10 @@
     </row>
     <row r="457" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C457">
         <v>8800</v>
@@ -23879,10 +23898,10 @@
     </row>
     <row r="458" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C458">
         <v>8800</v>
@@ -23923,10 +23942,10 @@
     </row>
     <row r="459" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C459">
         <v>8800</v>
@@ -23967,10 +23986,10 @@
     </row>
     <row r="460" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C460">
         <v>8800</v>
@@ -24011,10 +24030,10 @@
     </row>
     <row r="461" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C461">
         <v>5500</v>
@@ -24055,19 +24074,19 @@
     </row>
     <row r="462" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C462">
         <v>27600</v>
       </c>
       <c r="D462">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F462">
         <v>-1</v>
@@ -24099,19 +24118,19 @@
     </row>
     <row r="463" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C463">
         <v>15600</v>
       </c>
       <c r="D463">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F463">
         <v>-1</v>
@@ -24143,19 +24162,19 @@
     </row>
     <row r="464" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C464">
         <v>5600</v>
       </c>
       <c r="D464">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F464">
         <v>-1</v>
@@ -24187,10 +24206,10 @@
     </row>
     <row r="465" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C465">
         <v>27600</v>
@@ -24231,10 +24250,10 @@
     </row>
     <row r="466" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C466">
         <v>15600</v>
@@ -24275,10 +24294,10 @@
     </row>
     <row r="467" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C467">
         <v>5600</v>
@@ -24319,10 +24338,10 @@
     </row>
     <row r="468" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C468">
         <v>27600</v>
@@ -24363,10 +24382,10 @@
     </row>
     <row r="469" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C469">
         <v>15600</v>
@@ -24407,10 +24426,10 @@
     </row>
     <row r="470" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C470">
         <v>5600</v>
@@ -24451,10 +24470,10 @@
     </row>
     <row r="471" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C471">
         <v>35000</v>
@@ -24495,10 +24514,10 @@
     </row>
     <row r="472" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C472">
         <v>14300</v>
@@ -24539,10 +24558,10 @@
     </row>
     <row r="473" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C473">
         <v>4400</v>
@@ -24583,10 +24602,10 @@
     </row>
     <row r="474" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C474">
         <v>35000</v>
@@ -24627,10 +24646,10 @@
     </row>
     <row r="475" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C475">
         <v>14300</v>
@@ -24671,10 +24690,10 @@
     </row>
     <row r="476" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C476">
         <v>4400</v>
@@ -24715,10 +24734,10 @@
     </row>
     <row r="477" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C477">
         <v>35000</v>
@@ -24759,10 +24778,10 @@
     </row>
     <row r="478" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C478">
         <v>14300</v>
@@ -24803,10 +24822,10 @@
     </row>
     <row r="479" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C479">
         <v>4400</v>
@@ -24847,19 +24866,19 @@
     </row>
     <row r="480" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C480">
         <v>27000</v>
       </c>
       <c r="D480">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F480">
         <v>-1</v>
@@ -24891,19 +24910,19 @@
     </row>
     <row r="481" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C481">
         <v>11000</v>
       </c>
       <c r="D481">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F481">
         <v>-1</v>
@@ -24935,19 +24954,19 @@
     </row>
     <row r="482" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C482">
         <v>3400</v>
       </c>
       <c r="D482">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F482">
         <v>-1</v>
@@ -24979,10 +24998,10 @@
     </row>
     <row r="483" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C483">
         <v>27000</v>
@@ -25023,10 +25042,10 @@
     </row>
     <row r="484" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C484">
         <v>11000</v>
@@ -25067,10 +25086,10 @@
     </row>
     <row r="485" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C485">
         <v>3400</v>
@@ -25111,10 +25130,10 @@
     </row>
     <row r="486" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C486">
         <v>27000</v>
@@ -25155,10 +25174,10 @@
     </row>
     <row r="487" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C487">
         <v>11000</v>
@@ -25199,10 +25218,10 @@
     </row>
     <row r="488" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C488">
         <v>3400</v>
@@ -25243,10 +25262,10 @@
     </row>
     <row r="489" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C489">
         <v>50</v>
@@ -25287,10 +25306,10 @@
     </row>
     <row r="490" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C490">
         <v>50</v>
@@ -25331,10 +25350,10 @@
     </row>
     <row r="491" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C491">
         <v>50</v>
@@ -25375,10 +25394,10 @@
     </row>
     <row r="492" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C492">
         <v>4100</v>
@@ -25419,10 +25438,10 @@
     </row>
     <row r="493" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C493">
         <v>11100</v>
@@ -25463,10 +25482,10 @@
     </row>
     <row r="494" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C494">
         <v>20100</v>
@@ -25507,10 +25526,10 @@
     </row>
     <row r="495" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C495">
         <v>30800</v>
@@ -25551,10 +25570,10 @@
     </row>
     <row r="496" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C496">
         <v>8200</v>
@@ -25595,10 +25614,10 @@
     </row>
     <row r="497" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C497">
         <v>22200</v>
@@ -25639,10 +25658,10 @@
     </row>
     <row r="498" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C498">
         <v>40200</v>
@@ -25683,10 +25702,10 @@
     </row>
     <row r="499" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C499">
         <v>61500</v>
@@ -25727,10 +25746,10 @@
     </row>
     <row r="500" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C500">
         <v>5900</v>
@@ -25771,10 +25790,10 @@
     </row>
     <row r="501" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C501">
         <v>11500</v>
@@ -25815,10 +25834,10 @@
     </row>
     <row r="502" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C502">
         <v>18100</v>
@@ -25859,10 +25878,10 @@
     </row>
     <row r="503" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C503">
         <v>26000</v>
@@ -25903,10 +25922,10 @@
     </row>
     <row r="504" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C504">
         <v>11800</v>
@@ -25947,10 +25966,10 @@
     </row>
     <row r="505" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C505">
         <v>23000</v>
@@ -25991,10 +26010,10 @@
     </row>
     <row r="506" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C506">
         <v>36200</v>
@@ -26035,10 +26054,10 @@
     </row>
     <row r="507" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C507">
         <v>52000</v>
@@ -26079,10 +26098,10 @@
     </row>
     <row r="508" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C508">
         <v>9900</v>
@@ -26123,10 +26142,10 @@
     </row>
     <row r="509" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C509">
         <v>9900</v>
@@ -26167,10 +26186,10 @@
     </row>
     <row r="510" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C510">
         <v>1000</v>
@@ -26211,10 +26230,10 @@
     </row>
     <row r="511" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C511">
         <v>1000</v>
@@ -26255,10 +26274,10 @@
     </row>
     <row r="512" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C512">
         <v>1000</v>
@@ -26299,10 +26318,10 @@
     </row>
     <row r="513" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C513">
         <v>1000</v>
@@ -26343,10 +26362,10 @@
     </row>
     <row r="514" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C514">
         <v>1000</v>
@@ -26387,10 +26406,10 @@
     </row>
     <row r="515" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C515">
         <v>1000</v>
@@ -26431,10 +26450,10 @@
     </row>
     <row r="516" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C516">
         <v>1000</v>
@@ -26475,10 +26494,10 @@
     </row>
     <row r="517" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C517">
         <v>0</v>
@@ -26519,10 +26538,10 @@
     </row>
     <row r="518" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C518">
         <v>3000</v>
@@ -26563,10 +26582,10 @@
     </row>
     <row r="519" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C519">
         <v>7900</v>
@@ -26607,10 +26626,10 @@
     </row>
     <row r="520" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C520">
         <v>1200</v>
@@ -26651,10 +26670,10 @@
     </row>
     <row r="521" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C521">
         <v>2000</v>
@@ -26695,10 +26714,10 @@
     </row>
     <row r="522" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C522">
         <v>3000</v>
@@ -26739,10 +26758,10 @@
     </row>
     <row r="523" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C523">
         <v>4800</v>
@@ -26783,10 +26802,10 @@
     </row>
     <row r="524" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C524">
         <v>2900</v>
@@ -26827,10 +26846,10 @@
     </row>
     <row r="525" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C525">
         <v>2900</v>
@@ -26871,10 +26890,10 @@
     </row>
     <row r="526" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C526">
         <v>2900</v>
@@ -26915,10 +26934,10 @@
     </row>
     <row r="527" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C527">
         <v>2900</v>
@@ -26959,10 +26978,10 @@
     </row>
     <row r="528" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C528">
         <v>2900</v>
@@ -27003,10 +27022,10 @@
     </row>
     <row r="529" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C529">
         <v>2900</v>
@@ -27047,10 +27066,10 @@
     </row>
     <row r="530" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C530">
         <v>2900</v>
@@ -27091,10 +27110,10 @@
     </row>
     <row r="531" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C531">
         <v>2900</v>
@@ -27135,10 +27154,10 @@
     </row>
     <row r="532" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C532">
         <v>2900</v>
@@ -27179,10 +27198,10 @@
     </row>
     <row r="533" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C533">
         <v>2900</v>
@@ -27223,10 +27242,10 @@
     </row>
     <row r="534" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C534">
         <v>2900</v>
@@ -27267,10 +27286,10 @@
     </row>
     <row r="535" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C535">
         <v>2900</v>
@@ -27311,10 +27330,10 @@
     </row>
     <row r="536" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C536">
         <v>14900</v>
@@ -27355,10 +27374,10 @@
     </row>
     <row r="537" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C537">
         <v>2500</v>
@@ -27399,10 +27418,10 @@
     </row>
     <row r="538" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C538">
         <v>2500</v>
@@ -27443,19 +27462,19 @@
     </row>
     <row r="539" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C539">
         <v>2500</v>
       </c>
       <c r="D539">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F539">
         <v>-1</v>
@@ -27487,10 +27506,10 @@
     </row>
     <row r="540" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C540">
         <v>8800</v>
@@ -27531,10 +27550,10 @@
     </row>
     <row r="541" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C541">
         <v>8800</v>
@@ -27575,10 +27594,10 @@
     </row>
     <row r="542" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C542">
         <v>8800</v>
@@ -27618,11 +27637,11 @@
       </c>
     </row>
     <row r="543" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A543" t="s">
-        <v>1096</v>
+      <c r="A543" s="4" t="s">
+        <v>1112</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="C543">
         <v>31500</v>
@@ -27637,7 +27656,7 @@
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H543">
         <v>0</v>
@@ -27662,26 +27681,26 @@
       </c>
     </row>
     <row r="544" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A544" t="s">
-        <v>1098</v>
+      <c r="A544" s="4" t="s">
+        <v>1113</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="C544">
         <v>31500</v>
       </c>
       <c r="D544">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H544">
         <v>0</v>
@@ -27706,11 +27725,11 @@
       </c>
     </row>
     <row r="545" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A545" t="s">
-        <v>1100</v>
+      <c r="A545" s="4" t="s">
+        <v>1114</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="C545">
         <v>31500</v>
@@ -27725,7 +27744,7 @@
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H545">
         <v>0</v>
@@ -27750,20 +27769,20 @@
       </c>
     </row>
     <row r="546" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A546" t="s">
-        <v>1102</v>
+      <c r="A546" s="4" t="s">
+        <v>1115</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C546">
         <v>1100</v>
       </c>
       <c r="D546">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="F546">
         <v>-1</v>
@@ -27772,7 +27791,7 @@
         <v>0</v>
       </c>
       <c r="H546">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I546">
         <v>0</v>
@@ -27794,8 +27813,8 @@
       </c>
     </row>
     <row r="547" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A547" t="s">
-        <v>1104</v>
+      <c r="A547" s="3" t="s">
+        <v>1094</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>1105</v>
@@ -27816,7 +27835,7 @@
         <v>0</v>
       </c>
       <c r="H547">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I547">
         <v>0</v>
@@ -27838,17 +27857,17 @@
       </c>
     </row>
     <row r="548" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A548" t="s">
+      <c r="A548" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B548" s="2" t="s">
         <v>1106</v>
-      </c>
-      <c r="B548" s="2" t="s">
-        <v>1107</v>
       </c>
       <c r="C548">
         <v>16500</v>
       </c>
       <c r="D548">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>19</v>
@@ -27882,11 +27901,11 @@
       </c>
     </row>
     <row r="549" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A549" t="s">
-        <v>1108</v>
+      <c r="A549" s="3" t="s">
+        <v>1096</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C549">
         <v>300</v>
@@ -27904,7 +27923,7 @@
         <v>0</v>
       </c>
       <c r="H549">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I549">
         <v>0</v>
@@ -27926,11 +27945,11 @@
       </c>
     </row>
     <row r="550" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A550" t="s">
-        <v>1110</v>
+      <c r="A550" s="3" t="s">
+        <v>1097</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="C550">
         <v>550</v>
@@ -27948,7 +27967,7 @@
         <v>0</v>
       </c>
       <c r="H550">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I550">
         <v>0</v>
@@ -27971,10 +27990,10 @@
     </row>
     <row r="551" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1112</v>
+        <v>1098</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1113</v>
+        <v>1099</v>
       </c>
       <c r="C551">
         <v>450</v>
@@ -28015,16 +28034,16 @@
     </row>
     <row r="552" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1114</v>
+        <v>1100</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1115</v>
+        <v>1101</v>
       </c>
       <c r="C552">
         <v>1300</v>
       </c>
       <c r="D552">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>19</v>
@@ -28059,16 +28078,16 @@
     </row>
     <row r="553" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1116</v>
+        <v>1102</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1117</v>
+        <v>1103</v>
       </c>
       <c r="C553">
         <v>2100</v>
       </c>
       <c r="D553">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E553" s="1" t="s">
         <v>19</v>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95469090-8A5A-4BD1-B352-0D18D29ACB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D21F273-FC8F-4EF1-B80B-5A67FE771A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11631,10 +11631,10 @@
         <v>2200</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="F179">
         <v>-1</v>
@@ -11675,10 +11675,10 @@
         <v>300</v>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F180">
         <v>-1</v>
@@ -13479,10 +13479,10 @@
         <v>19800</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F221">
         <v>-1</v>
@@ -13831,10 +13831,10 @@
         <v>40</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F229">
         <v>-1</v>
@@ -13875,10 +13875,10 @@
         <v>40</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F230">
         <v>-1</v>
@@ -13963,10 +13963,10 @@
         <v>40</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F232">
         <v>-1</v>
@@ -14711,10 +14711,10 @@
         <v>10</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F249">
         <v>-1</v>
@@ -14755,10 +14755,10 @@
         <v>10</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F250">
         <v>-1</v>
@@ -14799,10 +14799,10 @@
         <v>10</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F251">
         <v>-1</v>
@@ -14843,10 +14843,10 @@
         <v>20</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F252">
         <v>-1</v>
@@ -14887,10 +14887,10 @@
         <v>20</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F253">
         <v>-1</v>
@@ -14931,10 +14931,10 @@
         <v>20</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="F254">
         <v>-1</v>
@@ -15767,7 +15767,7 @@
         <v>200</v>
       </c>
       <c r="D273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>210</v>
@@ -15811,7 +15811,7 @@
         <v>200</v>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>210</v>
@@ -15855,7 +15855,7 @@
         <v>200</v>
       </c>
       <c r="D275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>210</v>
@@ -16295,7 +16295,7 @@
         <v>200</v>
       </c>
       <c r="D285">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>210</v>
@@ -16339,7 +16339,7 @@
         <v>200</v>
       </c>
       <c r="D286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>210</v>
@@ -16383,7 +16383,7 @@
         <v>200</v>
       </c>
       <c r="D287">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>210</v>
@@ -16427,7 +16427,7 @@
         <v>200</v>
       </c>
       <c r="D288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>210</v>
@@ -16471,7 +16471,7 @@
         <v>200</v>
       </c>
       <c r="D289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>210</v>
@@ -16515,7 +16515,7 @@
         <v>200</v>
       </c>
       <c r="D290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>210</v>
@@ -16559,7 +16559,7 @@
         <v>200</v>
       </c>
       <c r="D291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>210</v>
@@ -16603,7 +16603,7 @@
         <v>200</v>
       </c>
       <c r="D292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>210</v>
@@ -16647,7 +16647,7 @@
         <v>200</v>
       </c>
       <c r="D293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>210</v>
@@ -25271,10 +25271,10 @@
         <v>50</v>
       </c>
       <c r="D489">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F489">
         <v>-1</v>
@@ -25315,10 +25315,10 @@
         <v>50</v>
       </c>
       <c r="D490">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F490">
         <v>-1</v>
@@ -25359,10 +25359,10 @@
         <v>50</v>
       </c>
       <c r="D491">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="F491">
         <v>-1</v>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F422A7-1010-4212-AA1E-862DFDACD00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B48FB12-1669-4EC6-8ED7-BD77C3DCDD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B48FB12-1669-4EC6-8ED7-BD77C3DCDD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E97EFB5-F2BF-43BC-A82F-DCA2742B086A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="276">
   <si>
     <t>string[64]</t>
   </si>
@@ -763,36 +763,6 @@
     <t>iycsa55</t>
   </si>
   <si>
-    <t>ircha01</t>
-  </si>
-  <si>
-    <t>ircha02</t>
-  </si>
-  <si>
-    <t>ircha03</t>
-  </si>
-  <si>
-    <t>ircha04</t>
-  </si>
-  <si>
-    <t>ircha05</t>
-  </si>
-  <si>
-    <t>ircha06</t>
-  </si>
-  <si>
-    <t>ircha07</t>
-  </si>
-  <si>
-    <t>ircha08</t>
-  </si>
-  <si>
-    <t>ircha10</t>
-  </si>
-  <si>
-    <t>ircha11</t>
-  </si>
-  <si>
     <t>ircja09</t>
   </si>
   <si>
@@ -848,6 +818,42 @@
   </si>
   <si>
     <t>ibcsb36</t>
+  </si>
+  <si>
+    <t>ircha13</t>
+  </si>
+  <si>
+    <t>ircha14</t>
+  </si>
+  <si>
+    <t>ircha15</t>
+  </si>
+  <si>
+    <t>ircha16</t>
+  </si>
+  <si>
+    <t>ircha17</t>
+  </si>
+  <si>
+    <t>ircha18</t>
+  </si>
+  <si>
+    <t>ircha19</t>
+  </si>
+  <si>
+    <t>ircha20</t>
+  </si>
+  <si>
+    <t>cash130</t>
+  </si>
+  <si>
+    <t>ircha22</t>
+  </si>
+  <si>
+    <t>ircha23</t>
+  </si>
+  <si>
+    <t>ircha24</t>
   </si>
 </sst>
 </file>
@@ -872,7 +878,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -893,7 +899,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -914,10 +920,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1254,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -1265,8 +1271,7 @@
     <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="14" width="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="17" max="18" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1365,7 +1370,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1409,7 +1414,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -1453,7 +1458,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C5">
         <v>505</v>
@@ -1497,7 +1502,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1541,7 +1546,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>150</v>
@@ -1585,7 +1590,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C8">
         <v>505</v>
@@ -1629,7 +1634,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1673,7 +1678,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>150</v>
@@ -1717,7 +1722,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C11">
         <v>505</v>
@@ -1764,7 +1769,7 @@
         <v>151</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1808,7 +1813,7 @@
         <v>152</v>
       </c>
       <c r="C13">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1852,7 +1857,7 @@
         <v>153</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1896,7 +1901,7 @@
         <v>154</v>
       </c>
       <c r="C15">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1940,7 +1945,7 @@
         <v>155</v>
       </c>
       <c r="C16">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1984,7 +1989,7 @@
         <v>156</v>
       </c>
       <c r="C17">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2028,7 +2033,7 @@
         <v>157</v>
       </c>
       <c r="C18">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2072,7 +2077,7 @@
         <v>158</v>
       </c>
       <c r="C19">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2116,7 +2121,7 @@
         <v>159</v>
       </c>
       <c r="C20">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2160,7 +2165,7 @@
         <v>160</v>
       </c>
       <c r="C21">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2204,7 +2209,7 @@
         <v>161</v>
       </c>
       <c r="C22">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2248,7 +2253,7 @@
         <v>162</v>
       </c>
       <c r="C23">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2292,7 +2297,7 @@
         <v>163</v>
       </c>
       <c r="C24">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2336,7 +2341,7 @@
         <v>164</v>
       </c>
       <c r="C25">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2380,7 +2385,7 @@
         <v>165</v>
       </c>
       <c r="C26">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2424,7 +2429,7 @@
         <v>166</v>
       </c>
       <c r="C27">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2468,7 +2473,7 @@
         <v>167</v>
       </c>
       <c r="C28">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2512,7 +2517,7 @@
         <v>168</v>
       </c>
       <c r="C29">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2556,7 +2561,7 @@
         <v>169</v>
       </c>
       <c r="C30">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2600,7 +2605,7 @@
         <v>170</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2644,7 +2649,7 @@
         <v>171</v>
       </c>
       <c r="C32">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2688,7 +2693,7 @@
         <v>172</v>
       </c>
       <c r="C33">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2732,7 +2737,7 @@
         <v>173</v>
       </c>
       <c r="C34">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2776,7 +2781,7 @@
         <v>174</v>
       </c>
       <c r="C35">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2820,7 +2825,7 @@
         <v>175</v>
       </c>
       <c r="C36">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2864,7 +2869,7 @@
         <v>176</v>
       </c>
       <c r="C37">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2908,7 +2913,7 @@
         <v>177</v>
       </c>
       <c r="C38">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2952,7 +2957,7 @@
         <v>178</v>
       </c>
       <c r="C39">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2996,7 +3001,7 @@
         <v>179</v>
       </c>
       <c r="C40">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3033,14 +3038,14 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="A41" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C41">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -3077,14 +3082,14 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" t="s">
         <v>60</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C42">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3121,14 +3126,14 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C43">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -3165,14 +3170,14 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" t="s">
         <v>62</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C44">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -3209,14 +3214,14 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="A45" t="s">
         <v>63</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C45">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -3253,14 +3258,14 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" t="s">
         <v>64</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C46">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -3297,14 +3302,14 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C47">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3341,14 +3346,14 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="A48" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C48">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3385,14 +3390,14 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="A49" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C49">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3429,14 +3434,14 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="A50" t="s">
         <v>68</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C50">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3480,7 +3485,7 @@
         <v>180</v>
       </c>
       <c r="C51">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3524,7 +3529,7 @@
         <v>181</v>
       </c>
       <c r="C52">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3568,7 +3573,7 @@
         <v>182</v>
       </c>
       <c r="C53">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3612,7 +3617,7 @@
         <v>183</v>
       </c>
       <c r="C54">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3656,7 +3661,7 @@
         <v>184</v>
       </c>
       <c r="C55">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3700,7 +3705,7 @@
         <v>185</v>
       </c>
       <c r="C56">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3744,7 +3749,7 @@
         <v>186</v>
       </c>
       <c r="C57">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3788,7 +3793,7 @@
         <v>187</v>
       </c>
       <c r="C58">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3832,7 +3837,7 @@
         <v>188</v>
       </c>
       <c r="C59">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3876,7 +3881,7 @@
         <v>189</v>
       </c>
       <c r="C60">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3920,7 +3925,7 @@
         <v>190</v>
       </c>
       <c r="C61">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3964,7 +3969,7 @@
         <v>191</v>
       </c>
       <c r="C62">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -4008,7 +4013,7 @@
         <v>192</v>
       </c>
       <c r="C63">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -4052,7 +4057,7 @@
         <v>193</v>
       </c>
       <c r="C64">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -4096,7 +4101,7 @@
         <v>194</v>
       </c>
       <c r="C65">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -4140,7 +4145,7 @@
         <v>195</v>
       </c>
       <c r="C66">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -4184,7 +4189,7 @@
         <v>196</v>
       </c>
       <c r="C67">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -4228,7 +4233,7 @@
         <v>197</v>
       </c>
       <c r="C68">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -4932,7 +4937,7 @@
         <v>213</v>
       </c>
       <c r="C84">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -6204,8 +6209,8 @@
       <c r="A113" t="s">
         <v>132</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>245</v>
+      <c r="B113" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="C113">
         <v>20</v>
@@ -6248,8 +6253,8 @@
       <c r="A114" t="s">
         <v>133</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>246</v>
+      <c r="B114" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="C114">
         <v>20</v>
@@ -6292,8 +6297,8 @@
       <c r="A115" t="s">
         <v>134</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>247</v>
+      <c r="B115" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="C115">
         <v>20</v>
@@ -6336,8 +6341,8 @@
       <c r="A116" t="s">
         <v>135</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>248</v>
+      <c r="B116" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="C116">
         <v>20</v>
@@ -6380,8 +6385,8 @@
       <c r="A117" t="s">
         <v>136</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>249</v>
+      <c r="B117" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -6424,8 +6429,8 @@
       <c r="A118" t="s">
         <v>137</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>250</v>
+      <c r="B118" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="C118">
         <v>20</v>
@@ -6468,8 +6473,8 @@
       <c r="A119" t="s">
         <v>138</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>251</v>
+      <c r="B119" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="C119">
         <v>20</v>
@@ -6512,8 +6517,8 @@
       <c r="A120" t="s">
         <v>139</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>252</v>
+      <c r="B120" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="C120">
         <v>20</v>
@@ -6556,8 +6561,8 @@
       <c r="A121" t="s">
         <v>140</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>253</v>
+      <c r="B121" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="C121">
         <v>20</v>
@@ -6600,8 +6605,8 @@
       <c r="A122" t="s">
         <v>141</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>254</v>
+      <c r="B122" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="C122">
         <v>20</v>
@@ -6644,11 +6649,11 @@
       <c r="A123" t="s">
         <v>142</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>260</v>
+      <c r="B123" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="C123">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -6689,10 +6694,10 @@
         <v>143</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C124">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -6733,10 +6738,10 @@
         <v>144</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C125">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -6777,10 +6782,10 @@
         <v>145</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C126">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -6821,10 +6826,10 @@
         <v>146</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C127">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -6865,10 +6870,10 @@
         <v>147</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C128">
-        <v>305</v>
+        <v>105</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -6909,10 +6914,10 @@
         <v>148</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="C129">
-        <v>505</v>
+        <v>305</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -6953,10 +6958,10 @@
         <v>149</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C130">
-        <v>1005</v>
+        <v>505</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -6997,42 +7002,86 @@
         <v>150</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C131">
+        <v>1005</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F131">
+        <v>-1</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>272</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C132">
         <v>150</v>
       </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F131">
-        <v>-1</v>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-      <c r="N131">
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F132">
+        <v>-1</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
         <v>0</v>
       </c>
     </row>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E97EFB5-F2BF-43BC-A82F-DCA2742B086A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B04DF5-1582-4588-BEEA-95FF83DB57F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4321,7 +4321,7 @@
         <v>199</v>
       </c>
       <c r="C70">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -4365,7 +4365,7 @@
         <v>200</v>
       </c>
       <c r="C71">
-        <v>211</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -4453,7 +4453,7 @@
         <v>202</v>
       </c>
       <c r="C73">
-        <v>213</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -4497,7 +4497,7 @@
         <v>203</v>
       </c>
       <c r="C74">
-        <v>214</v>
+        <v>2</v>
       </c>
       <c r="D74">
         <v>1</v>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B04DF5-1582-4588-BEEA-95FF83DB57F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04237B3-79D0-4EE1-96B4-142083D02E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="279">
   <si>
     <t>string[64]</t>
   </si>
@@ -854,6 +854,15 @@
   </si>
   <si>
     <t>ircha24</t>
+  </si>
+  <si>
+    <t>cash131</t>
+  </si>
+  <si>
+    <t>iybrd01</t>
+  </si>
+  <si>
+    <t>ne/be/0/0/0</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -7085,6 +7094,50 @@
         <v>0</v>
       </c>
     </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>276</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C133">
+        <v>5</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F133">
+        <v>-1</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04237B3-79D0-4EE1-96B4-142083D02E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5614D9AE-E9C7-4AAF-964F-2013B065B504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1778,7 +1778,7 @@
         <v>151</v>
       </c>
       <c r="C12">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>152</v>
       </c>
       <c r="C13">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1866,7 +1866,7 @@
         <v>153</v>
       </c>
       <c r="C14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1910,7 +1910,7 @@
         <v>154</v>
       </c>
       <c r="C15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1954,7 +1954,7 @@
         <v>155</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1998,7 +1998,7 @@
         <v>156</v>
       </c>
       <c r="C17">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2042,7 +2042,7 @@
         <v>157</v>
       </c>
       <c r="C18">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2086,7 +2086,7 @@
         <v>158</v>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2130,7 +2130,7 @@
         <v>159</v>
       </c>
       <c r="C20">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2174,7 +2174,7 @@
         <v>160</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2218,7 +2218,7 @@
         <v>161</v>
       </c>
       <c r="C22">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2262,7 +2262,7 @@
         <v>162</v>
       </c>
       <c r="C23">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2306,7 +2306,7 @@
         <v>163</v>
       </c>
       <c r="C24">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2350,7 +2350,7 @@
         <v>164</v>
       </c>
       <c r="C25">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>165</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2438,7 +2438,7 @@
         <v>166</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2482,7 +2482,7 @@
         <v>167</v>
       </c>
       <c r="C28">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2526,7 +2526,7 @@
         <v>168</v>
       </c>
       <c r="C29">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2570,7 +2570,7 @@
         <v>169</v>
       </c>
       <c r="C30">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2614,7 +2614,7 @@
         <v>170</v>
       </c>
       <c r="C31">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2658,7 +2658,7 @@
         <v>171</v>
       </c>
       <c r="C32">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2702,7 +2702,7 @@
         <v>172</v>
       </c>
       <c r="C33">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>173</v>
       </c>
       <c r="C34">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2790,7 +2790,7 @@
         <v>174</v>
       </c>
       <c r="C35">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         <v>175</v>
       </c>
       <c r="C36">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2878,7 +2878,7 @@
         <v>176</v>
       </c>
       <c r="C37">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2922,7 +2922,7 @@
         <v>177</v>
       </c>
       <c r="C38">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2966,7 +2966,7 @@
         <v>178</v>
       </c>
       <c r="C39">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -3010,7 +3010,7 @@
         <v>179</v>
       </c>
       <c r="C40">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3054,7 +3054,7 @@
         <v>254</v>
       </c>
       <c r="C41">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -3098,7 +3098,7 @@
         <v>255</v>
       </c>
       <c r="C42">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3142,7 +3142,7 @@
         <v>256</v>
       </c>
       <c r="C43">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -3186,7 +3186,7 @@
         <v>257</v>
       </c>
       <c r="C44">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -3230,7 +3230,7 @@
         <v>258</v>
       </c>
       <c r="C45">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -3274,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="C46">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -3318,7 +3318,7 @@
         <v>260</v>
       </c>
       <c r="C47">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>261</v>
       </c>
       <c r="C48">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3406,7 +3406,7 @@
         <v>262</v>
       </c>
       <c r="C49">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3450,7 +3450,7 @@
         <v>263</v>
       </c>
       <c r="C50">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3494,7 +3494,7 @@
         <v>180</v>
       </c>
       <c r="C51">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3538,7 +3538,7 @@
         <v>181</v>
       </c>
       <c r="C52">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3582,7 +3582,7 @@
         <v>182</v>
       </c>
       <c r="C53">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3626,7 +3626,7 @@
         <v>183</v>
       </c>
       <c r="C54">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3670,7 +3670,7 @@
         <v>184</v>
       </c>
       <c r="C55">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3714,7 +3714,7 @@
         <v>185</v>
       </c>
       <c r="C56">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         <v>186</v>
       </c>
       <c r="C57">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3802,7 +3802,7 @@
         <v>187</v>
       </c>
       <c r="C58">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3846,7 +3846,7 @@
         <v>188</v>
       </c>
       <c r="C59">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3890,7 +3890,7 @@
         <v>189</v>
       </c>
       <c r="C60">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3934,7 +3934,7 @@
         <v>190</v>
       </c>
       <c r="C61">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3978,7 +3978,7 @@
         <v>191</v>
       </c>
       <c r="C62">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -4022,7 +4022,7 @@
         <v>192</v>
       </c>
       <c r="C63">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -4066,7 +4066,7 @@
         <v>193</v>
       </c>
       <c r="C64">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>194</v>
       </c>
       <c r="C65">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -4154,7 +4154,7 @@
         <v>195</v>
       </c>
       <c r="C66">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -4198,7 +4198,7 @@
         <v>196</v>
       </c>
       <c r="C67">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -4242,7 +4242,7 @@
         <v>197</v>
       </c>
       <c r="C68">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -5650,7 +5650,7 @@
         <v>232</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -5694,7 +5694,7 @@
         <v>233</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -5738,7 +5738,7 @@
         <v>234</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -5914,7 +5914,7 @@
         <v>238</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -5958,7 +5958,7 @@
         <v>239</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -6002,7 +6002,7 @@
         <v>240</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -6222,7 +6222,7 @@
         <v>264</v>
       </c>
       <c r="C113">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -6266,7 +6266,7 @@
         <v>265</v>
       </c>
       <c r="C114">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -6310,7 +6310,7 @@
         <v>266</v>
       </c>
       <c r="C115">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -6354,7 +6354,7 @@
         <v>267</v>
       </c>
       <c r="C116">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -6398,7 +6398,7 @@
         <v>268</v>
       </c>
       <c r="C117">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -6442,7 +6442,7 @@
         <v>269</v>
       </c>
       <c r="C118">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -6486,7 +6486,7 @@
         <v>270</v>
       </c>
       <c r="C119">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -6530,7 +6530,7 @@
         <v>271</v>
       </c>
       <c r="C120">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -6574,7 +6574,7 @@
         <v>273</v>
       </c>
       <c r="C121">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         <v>274</v>
       </c>
       <c r="C122">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -6662,7 +6662,7 @@
         <v>275</v>
       </c>
       <c r="C123">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D123">
         <v>1</v>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5614D9AE-E9C7-4AAF-964F-2013B065B504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DFF500-58AD-4B7B-9E66-ACD76B5206EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="285">
   <si>
     <t>string[64]</t>
   </si>
@@ -863,6 +863,24 @@
   </si>
   <si>
     <t>ne/be/0/0/0</t>
+  </si>
+  <si>
+    <t>cash132</t>
+  </si>
+  <si>
+    <t>cash133</t>
+  </si>
+  <si>
+    <t>cash134</t>
+  </si>
+  <si>
+    <t>ipcsa34</t>
+  </si>
+  <si>
+    <t>ipcsa35</t>
+  </si>
+  <si>
+    <t>ipcsa36</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O133"/>
+  <dimension ref="A1:O136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -7094,7 +7112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>276</v>
       </c>
@@ -7135,6 +7153,138 @@
         <v>0</v>
       </c>
       <c r="N133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>279</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C134">
+        <v>5</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F134">
+        <v>-1</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>280</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C135">
+        <v>5</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F135">
+        <v>-1</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>281</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C136">
+        <v>5</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F136">
+        <v>-1</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
         <v>0</v>
       </c>
     </row>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DFF500-58AD-4B7B-9E66-ACD76B5206EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1383306-5313-4B0D-BD6C-8FFA8D7847FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4304,7 +4304,7 @@
         <v>198</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -4348,7 +4348,7 @@
         <v>199</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -4392,7 +4392,7 @@
         <v>200</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -4436,7 +4436,7 @@
         <v>201</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -4480,7 +4480,7 @@
         <v>202</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -4524,7 +4524,7 @@
         <v>203</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -5668,7 +5668,7 @@
         <v>232</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -5712,7 +5712,7 @@
         <v>233</v>
       </c>
       <c r="C101">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -5756,7 +5756,7 @@
         <v>234</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -5932,7 +5932,7 @@
         <v>238</v>
       </c>
       <c r="C106">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -5976,7 +5976,7 @@
         <v>239</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -6020,7 +6020,7 @@
         <v>240</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D108">
         <v>1</v>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1383306-5313-4B0D-BD6C-8FFA8D7847FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5465A3C4-3B52-4088-BFDD-DA7FB71348A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="295">
   <si>
     <t>string[64]</t>
   </si>
@@ -881,6 +881,36 @@
   </si>
   <si>
     <t>ipcsa36</t>
+  </si>
+  <si>
+    <t>cash135</t>
+  </si>
+  <si>
+    <t>cash136</t>
+  </si>
+  <si>
+    <t>cash137</t>
+  </si>
+  <si>
+    <t>cash138</t>
+  </si>
+  <si>
+    <t>cash139</t>
+  </si>
+  <si>
+    <t>ibcsb37</t>
+  </si>
+  <si>
+    <t>ibcsb38</t>
+  </si>
+  <si>
+    <t>ibcsb39</t>
+  </si>
+  <si>
+    <t>ibcsb40</t>
+  </si>
+  <si>
+    <t>ibcsb41</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O136"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -7288,6 +7318,226 @@
         <v>0</v>
       </c>
     </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>285</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C137">
+        <v>100</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F137">
+        <v>-1</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>286</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C138">
+        <v>100</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F138">
+        <v>-1</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>287</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C139">
+        <v>100</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F139">
+        <v>-1</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>288</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C140">
+        <v>100</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F140">
+        <v>-1</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>289</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C141">
+        <v>100</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F141">
+        <v>-1</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5465A3C4-3B52-4088-BFDD-DA7FB71348A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3AA848-26DA-4A36-AA62-9B4416800238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5970" yWindow="705" windowWidth="17565" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CashShop" sheetId="1" r:id="rId1"/>
@@ -898,19 +898,19 @@
     <t>cash139</t>
   </si>
   <si>
-    <t>ibcsb37</t>
-  </si>
-  <si>
-    <t>ibcsb38</t>
-  </si>
-  <si>
-    <t>ibcsb39</t>
-  </si>
-  <si>
-    <t>ibcsb40</t>
-  </si>
-  <si>
-    <t>ibcsb41</t>
+    <t>ibcsb42</t>
+  </si>
+  <si>
+    <t>ibcsb43</t>
+  </si>
+  <si>
+    <t>ibcsb44</t>
+  </si>
+  <si>
+    <t>ibcsb45</t>
+  </si>
+  <si>
+    <t>ibcsb46</t>
   </si>
 </sst>
 </file>
@@ -7322,7 +7322,7 @@
       <c r="A137" t="s">
         <v>285</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" t="s">
         <v>290</v>
       </c>
       <c r="C137">
@@ -7341,7 +7341,7 @@
         <v>0</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -7366,7 +7366,7 @@
       <c r="A138" t="s">
         <v>286</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" t="s">
         <v>291</v>
       </c>
       <c r="C138">
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -7410,7 +7410,7 @@
       <c r="A139" t="s">
         <v>287</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" t="s">
         <v>292</v>
       </c>
       <c r="C139">
@@ -7429,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -7454,7 +7454,7 @@
       <c r="A140" t="s">
         <v>288</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" t="s">
         <v>293</v>
       </c>
       <c r="C140">
@@ -7473,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -7498,7 +7498,7 @@
       <c r="A141" t="s">
         <v>289</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" t="s">
         <v>294</v>
       </c>
       <c r="C141">
@@ -7517,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141">
         <v>0</v>

--- a/gu_in/ItemCash.edf/CashShop.xlsx
+++ b/gu_in/ItemCash.edf/CashShop.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3AA848-26DA-4A36-AA62-9B4416800238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962A2B1A-942B-43C4-9098-E288A48BFEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5970" yWindow="705" windowWidth="17565" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CashShop" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="291">
   <si>
     <t>string[64]</t>
   </si>
@@ -640,12 +640,6 @@
     <t>ipcsb10</t>
   </si>
   <si>
-    <t>ipevn07</t>
-  </si>
-  <si>
-    <t>ipevn06</t>
-  </si>
-  <si>
     <t>ipdou01</t>
   </si>
   <si>
@@ -890,12 +884,6 @@
   </si>
   <si>
     <t>cash137</t>
-  </si>
-  <si>
-    <t>cash138</t>
-  </si>
-  <si>
-    <t>cash139</t>
   </si>
   <si>
     <t>ibcsb42</t>
@@ -1317,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -1427,7 +1415,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1445,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1471,7 +1459,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -1489,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1515,7 +1503,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C5">
         <v>505</v>
@@ -1559,7 +1547,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1577,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1603,7 +1591,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C7">
         <v>150</v>
@@ -1621,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1647,7 +1635,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C8">
         <v>505</v>
@@ -1691,7 +1679,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1709,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1735,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C10">
         <v>150</v>
@@ -1753,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1779,7 +1767,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C11">
         <v>505</v>
@@ -1841,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1885,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1929,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1973,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2017,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2061,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2149,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2193,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2237,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2281,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2325,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2369,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2413,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2457,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2501,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2545,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2589,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2633,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2677,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2721,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2765,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2809,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2853,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2897,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2941,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2985,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -3029,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -3073,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3099,7 +3087,7 @@
         <v>59</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -3117,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3143,7 +3131,7 @@
         <v>60</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -3161,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3187,7 +3175,7 @@
         <v>61</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -3205,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3231,7 +3219,7 @@
         <v>62</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -3249,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3275,7 +3263,7 @@
         <v>63</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C45">
         <v>100</v>
@@ -3293,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3319,7 +3307,7 @@
         <v>64</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -3337,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3363,7 +3351,7 @@
         <v>65</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -3381,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3407,7 +3395,7 @@
         <v>66</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -3425,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3451,7 +3439,7 @@
         <v>67</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C49">
         <v>100</v>
@@ -3469,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3495,7 +3483,7 @@
         <v>68</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -3513,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -4349,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4393,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4437,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4481,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -4525,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -4569,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -4598,7 +4586,7 @@
         <v>204</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -4607,7 +4595,7 @@
         <v>18</v>
       </c>
       <c r="F75">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -4642,7 +4630,7 @@
         <v>205</v>
       </c>
       <c r="C76">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -4686,7 +4674,7 @@
         <v>206</v>
       </c>
       <c r="C77">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4695,7 +4683,7 @@
         <v>18</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -4730,7 +4718,7 @@
         <v>207</v>
       </c>
       <c r="C78">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -4774,7 +4762,7 @@
         <v>208</v>
       </c>
       <c r="C79">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -4818,7 +4806,7 @@
         <v>209</v>
       </c>
       <c r="C80">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -4862,7 +4850,7 @@
         <v>210</v>
       </c>
       <c r="C81">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4912,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82">
         <v>-1</v>
@@ -4947,16 +4935,16 @@
         <v>101</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C83">
+        <v>10</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C83">
-        <v>300</v>
-      </c>
-      <c r="D83">
-        <v>1</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F83">
         <v>-1</v>
@@ -4991,16 +4979,16 @@
         <v>102</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C84">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F84">
         <v>-1</v>
@@ -5030,7 +5018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>103</v>
       </c>
@@ -5038,13 +5026,13 @@
         <v>215</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>214</v>
+        <v>22</v>
       </c>
       <c r="F85">
         <v>-1</v>
@@ -5053,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -5082,13 +5070,13 @@
         <v>216</v>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F86">
         <v>-1</v>
@@ -5097,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -5118,7 +5106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>105</v>
       </c>
@@ -5126,13 +5114,13 @@
         <v>217</v>
       </c>
       <c r="C87">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F87">
         <v>-1</v>
@@ -5185,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -5211,7 +5199,7 @@
         <v>107</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -5220,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="F89">
         <v>-1</v>
@@ -5229,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -5255,7 +5243,7 @@
         <v>108</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -5264,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="F90">
         <v>-1</v>
@@ -5273,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="H90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -5299,7 +5287,7 @@
         <v>109</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -5308,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F91">
         <v>-1</v>
@@ -5317,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -5352,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>223</v>
+        <v>118</v>
       </c>
       <c r="F92">
         <v>-1</v>
@@ -5361,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -5396,7 +5384,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>223</v>
+        <v>118</v>
       </c>
       <c r="F93">
         <v>-1</v>
@@ -5405,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -5449,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -5484,7 +5472,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="F95">
         <v>-1</v>
@@ -5493,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -5528,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="F96">
         <v>-1</v>
@@ -5537,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -5572,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F97">
         <v>-1</v>
@@ -5581,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -5616,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F98">
         <v>-1</v>
@@ -5625,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -5660,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F99">
         <v>-1</v>
@@ -5669,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -5704,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F100">
         <v>-1</v>
@@ -5713,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -5742,13 +5730,13 @@
         <v>233</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="F101">
         <v>-1</v>
@@ -5757,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -5786,13 +5774,13 @@
         <v>234</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="F102">
         <v>-1</v>
@@ -5801,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -5845,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -5874,13 +5862,13 @@
         <v>236</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="F104">
         <v>-1</v>
@@ -5889,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -5918,13 +5906,13 @@
         <v>237</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="F105">
         <v>-1</v>
@@ -5933,7 +5921,7 @@
         <v>0</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -5977,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="H106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -6006,13 +5994,13 @@
         <v>239</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="F107">
         <v>-1</v>
@@ -6021,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -6050,13 +6038,13 @@
         <v>240</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="F108">
         <v>-1</v>
@@ -6065,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="H108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -6094,13 +6082,13 @@
         <v>241</v>
       </c>
       <c r="C109">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F109">
         <v>-1</v>
@@ -6178,17 +6166,17 @@
       <c r="A111" t="s">
         <v>130</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>243</v>
+      <c r="B111" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="C111">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F111">
         <v>-1</v>
@@ -6222,17 +6210,17 @@
       <c r="A112" t="s">
         <v>131</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>244</v>
+      <c r="B112" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="C112">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F112">
         <v>-1</v>
@@ -6531,7 +6519,7 @@
         <v>138</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C119">
         <v>60</v>
@@ -6575,7 +6563,7 @@
         <v>139</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C120">
         <v>60</v>
@@ -6662,11 +6650,11 @@
       <c r="A122" t="s">
         <v>141</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>274</v>
+      <c r="B122" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="C122">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -6706,11 +6694,11 @@
       <c r="A123" t="s">
         <v>142</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>275</v>
+      <c r="B123" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="C123">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -6754,7 +6742,7 @@
         <v>250</v>
       </c>
       <c r="C124">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -6798,7 +6786,7 @@
         <v>251</v>
       </c>
       <c r="C125">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -6839,10 +6827,10 @@
         <v>145</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C126">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -6883,10 +6871,10 @@
         <v>146</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C127">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -6930,7 +6918,7 @@
         <v>247</v>
       </c>
       <c r="C128">
-        <v>105</v>
+        <v>505</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -6971,10 +6959,10 @@
         <v>148</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C129">
-        <v>305</v>
+        <v>1005</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -7015,10 +7003,10 @@
         <v>149</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C130">
-        <v>505</v>
+        <v>150</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -7054,21 +7042,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>246</v>
+      <c r="B131" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="C131">
-        <v>1005</v>
+        <v>5</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="F131">
         <v>-1</v>
@@ -7100,19 +7088,19 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>272</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>245</v>
+        <v>270</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="C132">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="D132">
         <v>1</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="F132">
         <v>-1</v>
@@ -7142,12 +7130,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C133">
         <v>5</v>
@@ -7156,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F133">
         <v>-1</v>
@@ -7188,7 +7176,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>282</v>
@@ -7200,7 +7188,7 @@
         <v>1</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F134">
         <v>-1</v>
@@ -7232,19 +7220,19 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>280</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
+      </c>
+      <c r="B135" t="s">
+        <v>286</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D135">
         <v>1</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="F135">
         <v>-1</v>
@@ -7276,19 +7264,19 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>281</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
+      </c>
+      <c r="B136" t="s">
+        <v>287</v>
       </c>
       <c r="C136">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="F136">
         <v>-1</v>
@@ -7320,10 +7308,10 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B137" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -7364,10 +7352,10 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C138">
         <v>100</v>
@@ -7408,10 +7396,10 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B139" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C139">
         <v>100</v>
@@ -7447,94 +7435,6 @@
         <v>0</v>
       </c>
       <c r="N139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>288</v>
-      </c>
-      <c r="B140" t="s">
-        <v>293</v>
-      </c>
-      <c r="C140">
-        <v>100</v>
-      </c>
-      <c r="D140">
-        <v>1</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F140">
-        <v>-1</v>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>289</v>
-      </c>
-      <c r="B141" t="s">
-        <v>294</v>
-      </c>
-      <c r="C141">
-        <v>100</v>
-      </c>
-      <c r="D141">
-        <v>1</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F141">
-        <v>-1</v>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141">
         <v>0</v>
       </c>
     </row>
